--- a/Output Coni/output_wide_fit_metrics.xlsx
+++ b/Output Coni/output_wide_fit_metrics.xlsx
@@ -175,44 +175,44 @@
   <dimension ref="A1:AL65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.28515625" customWidth="true"/>
-    <col min="2" max="2" width="11.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="11.7109375" customWidth="true"/>
-    <col min="5" max="5" width="11.7109375" customWidth="true"/>
-    <col min="6" max="6" width="11.7109375" customWidth="true"/>
-    <col min="7" max="7" width="11.7109375" customWidth="true"/>
-    <col min="8" max="8" width="11.7109375" customWidth="true"/>
-    <col min="9" max="9" width="11.7109375" customWidth="true"/>
-    <col min="10" max="10" width="11.7109375" customWidth="true"/>
-    <col min="11" max="11" width="11.7109375" customWidth="true"/>
-    <col min="12" max="12" width="11.7109375" customWidth="true"/>
-    <col min="13" max="13" width="11.7109375" customWidth="true"/>
-    <col min="14" max="14" width="11.7109375" customWidth="true"/>
-    <col min="15" max="15" width="11.7109375" customWidth="true"/>
-    <col min="16" max="16" width="11.7109375" customWidth="true"/>
-    <col min="17" max="17" width="11.7109375" customWidth="true"/>
-    <col min="18" max="18" width="11.7109375" customWidth="true"/>
-    <col min="19" max="19" width="11.7109375" customWidth="true"/>
-    <col min="20" max="20" width="11.7109375" customWidth="true"/>
-    <col min="21" max="21" width="11.7109375" customWidth="true"/>
-    <col min="22" max="22" width="11.7109375" customWidth="true"/>
-    <col min="23" max="23" width="11.7109375" customWidth="true"/>
-    <col min="24" max="24" width="11.7109375" customWidth="true"/>
-    <col min="25" max="25" width="11.7109375" customWidth="true"/>
-    <col min="26" max="26" width="11.7109375" customWidth="true"/>
-    <col min="27" max="27" width="11.7109375" customWidth="true"/>
-    <col min="28" max="28" width="11.7109375" customWidth="true"/>
-    <col min="29" max="29" width="11.7109375" customWidth="true"/>
-    <col min="30" max="30" width="11.7109375" customWidth="true"/>
-    <col min="31" max="31" width="11.7109375" customWidth="true"/>
-    <col min="32" max="32" width="11.7109375" customWidth="true"/>
-    <col min="33" max="33" width="11.7109375" customWidth="true"/>
-    <col min="34" max="34" width="11.7109375" customWidth="true"/>
-    <col min="35" max="35" width="11.7109375" customWidth="true"/>
-    <col min="36" max="36" width="11.7109375" customWidth="true"/>
-    <col min="37" max="37" width="11.7109375" customWidth="true"/>
-    <col min="38" max="38" width="6.28515625" customWidth="true"/>
+    <col min="1" max="1" width="9.21875" customWidth="true"/>
+    <col min="2" max="2" width="11.5546875" customWidth="true"/>
+    <col min="3" max="3" width="11.5546875" customWidth="true"/>
+    <col min="4" max="4" width="11.5546875" customWidth="true"/>
+    <col min="5" max="5" width="11.5546875" customWidth="true"/>
+    <col min="6" max="6" width="11.5546875" customWidth="true"/>
+    <col min="7" max="7" width="11.5546875" customWidth="true"/>
+    <col min="8" max="8" width="11.5546875" customWidth="true"/>
+    <col min="9" max="9" width="11.5546875" customWidth="true"/>
+    <col min="10" max="10" width="11.5546875" customWidth="true"/>
+    <col min="11" max="11" width="11.5546875" customWidth="true"/>
+    <col min="12" max="12" width="11.5546875" customWidth="true"/>
+    <col min="13" max="13" width="11.5546875" customWidth="true"/>
+    <col min="14" max="14" width="11.5546875" customWidth="true"/>
+    <col min="15" max="15" width="11.5546875" customWidth="true"/>
+    <col min="16" max="16" width="11.5546875" customWidth="true"/>
+    <col min="17" max="17" width="11.5546875" customWidth="true"/>
+    <col min="18" max="18" width="11.5546875" customWidth="true"/>
+    <col min="19" max="19" width="11.5546875" customWidth="true"/>
+    <col min="20" max="20" width="11.5546875" customWidth="true"/>
+    <col min="21" max="21" width="11.5546875" customWidth="true"/>
+    <col min="22" max="22" width="11.5546875" customWidth="true"/>
+    <col min="23" max="23" width="11.5546875" customWidth="true"/>
+    <col min="24" max="24" width="11.5546875" customWidth="true"/>
+    <col min="25" max="25" width="11.5546875" customWidth="true"/>
+    <col min="26" max="26" width="11.5546875" customWidth="true"/>
+    <col min="27" max="27" width="11.5546875" customWidth="true"/>
+    <col min="28" max="28" width="11.5546875" customWidth="true"/>
+    <col min="29" max="29" width="11.5546875" customWidth="true"/>
+    <col min="30" max="30" width="11.5546875" customWidth="true"/>
+    <col min="31" max="31" width="11.5546875" customWidth="true"/>
+    <col min="32" max="32" width="11.5546875" customWidth="true"/>
+    <col min="33" max="33" width="11.5546875" customWidth="true"/>
+    <col min="34" max="34" width="11.5546875" customWidth="true"/>
+    <col min="35" max="35" width="11.5546875" customWidth="true"/>
+    <col min="36" max="36" width="11.5546875" customWidth="true"/>
+    <col min="37" max="37" width="11.5546875" customWidth="true"/>
+    <col min="38" max="38" width="5.6640625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -336,112 +336,112 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C2" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D2" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E2" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F2" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G2" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H2" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I2" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J2" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K2" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L2" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M2" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N2" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O2" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P2" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q2" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R2" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S2" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T2" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U2" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V2" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W2" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X2" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y2" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z2" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA2" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB2" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC2" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD2" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE2" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF2" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG2" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH2" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI2" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ2" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK2" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL2" s="0">
         <v>1</v>
@@ -452,112 +452,112 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>11.090362982992399</v>
+        <v>11.090364961702299</v>
       </c>
       <c r="C3" s="0">
-        <v>26.180725965984902</v>
+        <v>26.180729923404598</v>
       </c>
       <c r="D3" s="0">
-        <v>29.923127987800701</v>
+        <v>29.923131945220401</v>
       </c>
       <c r="E3" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F3" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G3" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H3" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I3" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J3" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K3" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L3" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M3" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N3" s="0">
-        <v>2.5308074976298398</v>
+        <v>11.090362984902301</v>
       </c>
       <c r="O3" s="0">
-        <v>9.0616149952596903</v>
+        <v>26.180725969804499</v>
       </c>
       <c r="P3" s="0">
-        <v>12.8040170170755</v>
+        <v>29.923127991620301</v>
       </c>
       <c r="Q3" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R3" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S3" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T3" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U3" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V3" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W3" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X3" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y3" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z3" s="0">
-        <v>2.3448280767436298</v>
+        <v>11.090362978949001</v>
       </c>
       <c r="AA3" s="0">
-        <v>8.6896561534872507</v>
+        <v>26.180725957898101</v>
       </c>
       <c r="AB3" s="0">
-        <v>12.432058175303</v>
+        <v>29.923127979713801</v>
       </c>
       <c r="AC3" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD3" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE3" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF3" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG3" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH3" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI3" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ3" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK3" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL3" s="0">
         <v>1</v>
@@ -568,112 +568,112 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>29.4632986813649</v>
+        <v>29.463300281358599</v>
       </c>
       <c r="C4" s="0">
-        <v>62.9265973627299</v>
+        <v>62.926600562717297</v>
       </c>
       <c r="D4" s="0">
-        <v>66.6689993845457</v>
+        <v>66.669002584533004</v>
       </c>
       <c r="E4" s="0">
+        <v>31.367183074117499</v>
+      </c>
+      <c r="F4" s="0">
+        <v>68.734366148234997</v>
+      </c>
+      <c r="G4" s="0">
+        <v>74.3479691809587</v>
+      </c>
+      <c r="H4" s="0">
+        <v>29.4632986813704</v>
+      </c>
+      <c r="I4" s="0">
+        <v>64.926597362740907</v>
+      </c>
+      <c r="J4" s="0">
+        <v>70.540200395464495</v>
+      </c>
+      <c r="K4" s="0">
+        <v>31.3671818741302</v>
+      </c>
+      <c r="L4" s="0">
+        <v>70.734363748260407</v>
+      </c>
+      <c r="M4" s="0">
+        <v>78.219167791891905</v>
+      </c>
+      <c r="N4" s="0">
+        <v>29.4633002813605</v>
+      </c>
+      <c r="O4" s="0">
+        <v>62.926600562721099</v>
+      </c>
+      <c r="P4" s="0">
+        <v>66.669002584536898</v>
+      </c>
+      <c r="Q4" s="0">
+        <v>31.367181554295499</v>
+      </c>
+      <c r="R4" s="0">
+        <v>68.734363108590998</v>
+      </c>
+      <c r="S4" s="0">
+        <v>74.3479661413147</v>
+      </c>
+      <c r="T4" s="0">
+        <v>29.463300281360102</v>
+      </c>
+      <c r="U4" s="0">
+        <v>64.926600562720196</v>
+      </c>
+      <c r="V4" s="0">
+        <v>70.540203595443799</v>
+      </c>
+      <c r="W4" s="0">
+        <v>31.3671830741193</v>
+      </c>
+      <c r="X4" s="0">
+        <v>70.734366148238493</v>
+      </c>
+      <c r="Y4" s="0">
+        <v>78.219170191870106</v>
+      </c>
+      <c r="Z4" s="0">
+        <v>29.463298681373399</v>
+      </c>
+      <c r="AA4" s="0">
+        <v>62.926597362746797</v>
+      </c>
+      <c r="AB4" s="0">
+        <v>66.668999384562596</v>
+      </c>
+      <c r="AC4" s="0">
         <v>31.367181554121299</v>
       </c>
-      <c r="F4" s="0">
+      <c r="AD4" s="0">
         <v>68.734363108242604</v>
       </c>
-      <c r="G4" s="0">
+      <c r="AE4" s="0">
         <v>74.347966140966307</v>
       </c>
-      <c r="H4" s="0">
-        <v>29.463298686580298</v>
-      </c>
-      <c r="I4" s="0">
-        <v>64.926597373160504</v>
-      </c>
-      <c r="J4" s="0">
-        <v>70.540200405884207</v>
-      </c>
-      <c r="K4" s="0">
-        <v>31.3671830742589</v>
-      </c>
-      <c r="L4" s="0">
-        <v>70.734366148517793</v>
-      </c>
-      <c r="M4" s="0">
-        <v>78.219170192149406</v>
-      </c>
-      <c r="N4" s="0">
-        <v>29.192281105641001</v>
-      </c>
-      <c r="O4" s="0">
-        <v>62.384562211282002</v>
-      </c>
-      <c r="P4" s="0">
-        <v>66.126964233097794</v>
-      </c>
-      <c r="Q4" s="0">
-        <v>31.0031859455394</v>
-      </c>
-      <c r="R4" s="0">
-        <v>68.006371891078899</v>
-      </c>
-      <c r="S4" s="0">
-        <v>73.619974923802602</v>
-      </c>
-      <c r="T4" s="0">
-        <v>29.2052394877301</v>
-      </c>
-      <c r="U4" s="0">
-        <v>64.410478975460293</v>
-      </c>
-      <c r="V4" s="0">
-        <v>70.024082008183996</v>
-      </c>
-      <c r="W4" s="0">
-        <v>31.003185944666601</v>
-      </c>
-      <c r="X4" s="0">
-        <v>70.006371889333195</v>
-      </c>
-      <c r="Y4" s="0">
-        <v>77.491175932964794</v>
-      </c>
-      <c r="Z4" s="0">
-        <v>29.045924925091899</v>
-      </c>
-      <c r="AA4" s="0">
-        <v>62.091849850183799</v>
-      </c>
-      <c r="AB4" s="0">
-        <v>65.834251871999598</v>
-      </c>
-      <c r="AC4" s="0">
-        <v>30.835111258711901</v>
-      </c>
-      <c r="AD4" s="0">
-        <v>67.670222517423795</v>
-      </c>
-      <c r="AE4" s="0">
-        <v>73.283825550147498</v>
-      </c>
       <c r="AF4" s="0">
-        <v>29.369384353872501</v>
+        <v>29.463300281356801</v>
       </c>
       <c r="AG4" s="0">
-        <v>64.738768707745095</v>
+        <v>64.926600562713602</v>
       </c>
       <c r="AH4" s="0">
-        <v>70.352371740468797</v>
+        <v>70.540203595437305</v>
       </c>
       <c r="AI4" s="0">
-        <v>30.835111251287799</v>
+        <v>31.3671818741214</v>
       </c>
       <c r="AJ4" s="0">
-        <v>69.670222502575598</v>
+        <v>70.734363748242799</v>
       </c>
       <c r="AK4" s="0">
-        <v>77.155026546207196</v>
+        <v>78.219167791874298</v>
       </c>
       <c r="AL4" s="0">
         <v>1</v>
@@ -684,112 +684,112 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>23.8834503365253</v>
+        <v>23.883451936515701</v>
       </c>
       <c r="C5" s="0">
-        <v>51.7669006730506</v>
+        <v>51.766903873031303</v>
       </c>
       <c r="D5" s="0">
-        <v>55.5093026948663</v>
+        <v>55.509305894847103</v>
       </c>
       <c r="E5" s="0">
-        <v>31.367181494119901</v>
+        <v>31.3671814941181</v>
       </c>
       <c r="F5" s="0">
-        <v>68.734362988239894</v>
+        <v>68.734362988236299</v>
       </c>
       <c r="G5" s="0">
-        <v>74.347966020963597</v>
+        <v>74.347966020960001</v>
       </c>
       <c r="H5" s="0">
-        <v>23.883449956535699</v>
+        <v>23.883450341346801</v>
       </c>
       <c r="I5" s="0">
-        <v>53.766899913071498</v>
+        <v>53.766900682693702</v>
       </c>
       <c r="J5" s="0">
-        <v>59.380502945795101</v>
+        <v>59.380503715417298</v>
       </c>
       <c r="K5" s="0">
-        <v>31.367183474119301</v>
+        <v>31.367181874121201</v>
       </c>
       <c r="L5" s="0">
-        <v>70.734366948238701</v>
+        <v>70.734363748242501</v>
       </c>
       <c r="M5" s="0">
-        <v>78.2191709918702</v>
+        <v>78.219167791874</v>
       </c>
       <c r="N5" s="0">
-        <v>23.5532300880731</v>
+        <v>23.883450336524501</v>
       </c>
       <c r="O5" s="0">
-        <v>51.1064601761463</v>
+        <v>51.766900673049001</v>
       </c>
       <c r="P5" s="0">
-        <v>54.848862197961999</v>
+        <v>55.509302694864701</v>
       </c>
       <c r="Q5" s="0">
-        <v>28.8210896079812</v>
+        <v>31.367181874124402</v>
       </c>
       <c r="R5" s="0">
-        <v>63.6421792159624</v>
+        <v>68.734363748248796</v>
       </c>
       <c r="S5" s="0">
-        <v>69.255782248686103</v>
+        <v>74.347966780972499</v>
       </c>
       <c r="T5" s="0">
-        <v>23.35124845072</v>
+        <v>23.883450936769101</v>
       </c>
       <c r="U5" s="0">
-        <v>52.702496901440099</v>
+        <v>53.766901873538202</v>
       </c>
       <c r="V5" s="0">
-        <v>58.316099934163802</v>
+        <v>59.380504906261898</v>
       </c>
       <c r="W5" s="0">
-        <v>28.821089607937498</v>
+        <v>31.367181874123801</v>
       </c>
       <c r="X5" s="0">
-        <v>65.642179215875004</v>
+        <v>70.734363748247503</v>
       </c>
       <c r="Y5" s="0">
-        <v>73.126983259506503</v>
+        <v>78.219167791879102</v>
       </c>
       <c r="Z5" s="0">
-        <v>23.635597553343199</v>
+        <v>23.883450336521399</v>
       </c>
       <c r="AA5" s="0">
-        <v>51.271195106686399</v>
+        <v>51.766900673042798</v>
       </c>
       <c r="AB5" s="0">
-        <v>55.013597128502198</v>
+        <v>55.509302694858597</v>
       </c>
       <c r="AC5" s="0">
-        <v>30.782139117332701</v>
+        <v>31.367181874122299</v>
       </c>
       <c r="AD5" s="0">
-        <v>67.564278234665494</v>
+        <v>68.734363748244604</v>
       </c>
       <c r="AE5" s="0">
-        <v>73.177881267389097</v>
+        <v>74.347966780968306</v>
       </c>
       <c r="AF5" s="0">
-        <v>23.8662890221932</v>
+        <v>23.866289021319002</v>
       </c>
       <c r="AG5" s="0">
-        <v>53.732578044386401</v>
+        <v>53.732578042637897</v>
       </c>
       <c r="AH5" s="0">
-        <v>59.346181077110003</v>
+        <v>59.346181075361599</v>
       </c>
       <c r="AI5" s="0">
-        <v>30.782139112221198</v>
+        <v>31.367181874114902</v>
       </c>
       <c r="AJ5" s="0">
-        <v>69.564278224442504</v>
+        <v>70.734363748229796</v>
       </c>
       <c r="AK5" s="0">
-        <v>77.049082268074102</v>
+        <v>78.219167791861395</v>
       </c>
       <c r="AL5" s="0">
         <v>1</v>
@@ -800,112 +800,112 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C6" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D6" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E6" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F6" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G6" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H6" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I6" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J6" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K6" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L6" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M6" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N6" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O6" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P6" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q6" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R6" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S6" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T6" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U6" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V6" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W6" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X6" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y6" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z6" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA6" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB6" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC6" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD6" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE6" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF6" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG6" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH6" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI6" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ6" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK6" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL6" s="0">
         <v>1</v>
@@ -916,112 +916,112 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C7" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D7" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E7" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F7" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G7" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H7" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I7" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J7" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K7" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L7" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M7" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N7" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O7" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P7" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q7" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R7" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S7" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T7" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U7" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V7" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W7" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X7" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y7" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z7" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA7" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB7" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC7" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD7" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE7" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF7" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG7" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH7" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI7" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ7" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK7" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL7" s="0">
         <v>1</v>
@@ -1032,112 +1032,112 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C8" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D8" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E8" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F8" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G8" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H8" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I8" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J8" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K8" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L8" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M8" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N8" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O8" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P8" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q8" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R8" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S8" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T8" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U8" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V8" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W8" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X8" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y8" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z8" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA8" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB8" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC8" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD8" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE8" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF8" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG8" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH8" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI8" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ8" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK8" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL8" s="0">
         <v>1</v>
@@ -1148,112 +1148,112 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>22.561559041328898</v>
+        <v>22.561559041328799</v>
       </c>
       <c r="C9" s="0">
-        <v>49.123118082657797</v>
+        <v>49.123118082657498</v>
       </c>
       <c r="D9" s="0">
-        <v>52.865520104473603</v>
+        <v>52.865520104473298</v>
       </c>
       <c r="E9" s="0">
-        <v>29.701875523475401</v>
+        <v>29.701875523476101</v>
       </c>
       <c r="F9" s="0">
-        <v>65.403751046950902</v>
+        <v>65.403751046952195</v>
       </c>
       <c r="G9" s="0">
-        <v>71.017354079674504</v>
+        <v>71.017354079675897</v>
       </c>
       <c r="H9" s="0">
-        <v>22.561559041355999</v>
+        <v>22.561559041359299</v>
       </c>
       <c r="I9" s="0">
-        <v>51.123118082712097</v>
+        <v>51.123118082718598</v>
       </c>
       <c r="J9" s="0">
-        <v>56.736721115435699</v>
+        <v>56.7367211154423</v>
       </c>
       <c r="K9" s="0">
-        <v>29.701875523479799</v>
+        <v>29.701875523474602</v>
       </c>
       <c r="L9" s="0">
-        <v>67.403751046959698</v>
+        <v>67.403751046949196</v>
       </c>
       <c r="M9" s="0">
-        <v>74.888555090591197</v>
+        <v>74.888555090580795</v>
       </c>
       <c r="N9" s="0">
-        <v>16.668373575648999</v>
+        <v>22.561558741390701</v>
       </c>
       <c r="O9" s="0">
-        <v>37.336747151297999</v>
+        <v>49.123117482781502</v>
       </c>
       <c r="P9" s="0">
-        <v>41.079149173113798</v>
+        <v>52.865519504597202</v>
       </c>
       <c r="Q9" s="0">
-        <v>27.006355736987501</v>
+        <v>29.7018759035128</v>
       </c>
       <c r="R9" s="0">
-        <v>60.012711473975003</v>
+        <v>65.4037518070255</v>
       </c>
       <c r="S9" s="0">
-        <v>65.626314506698606</v>
+        <v>71.017354839749203</v>
       </c>
       <c r="T9" s="0">
-        <v>21.3808761676049</v>
+        <v>22.561560641308699</v>
       </c>
       <c r="U9" s="0">
-        <v>48.761752335209799</v>
+        <v>51.123121282617397</v>
       </c>
       <c r="V9" s="0">
-        <v>54.375355367933501</v>
+        <v>56.7367243153411</v>
       </c>
       <c r="W9" s="0">
-        <v>27.006355736986599</v>
+        <v>29.701875903512299</v>
       </c>
       <c r="X9" s="0">
-        <v>62.012711473973198</v>
+        <v>67.403751807024506</v>
       </c>
       <c r="Y9" s="0">
-        <v>69.497515517604796</v>
+        <v>74.888555850656104</v>
       </c>
       <c r="Z9" s="0">
-        <v>18.022162380098301</v>
+        <v>22.5615606397633</v>
       </c>
       <c r="AA9" s="0">
-        <v>40.044324760196602</v>
+        <v>49.123121279526501</v>
       </c>
       <c r="AB9" s="0">
-        <v>43.786726782012302</v>
+        <v>52.8655233013423</v>
       </c>
       <c r="AC9" s="0">
-        <v>26.704049468084701</v>
+        <v>29.7018757034805</v>
       </c>
       <c r="AD9" s="0">
-        <v>59.408098936169402</v>
+        <v>65.403751406960893</v>
       </c>
       <c r="AE9" s="0">
-        <v>65.021701968893098</v>
+        <v>71.017354439684595</v>
       </c>
       <c r="AF9" s="0">
-        <v>22.0943443456563</v>
+        <v>22.561560641307601</v>
       </c>
       <c r="AG9" s="0">
-        <v>50.188688691312599</v>
+        <v>51.123121282615301</v>
       </c>
       <c r="AH9" s="0">
-        <v>55.802291724036301</v>
+        <v>56.736724315339004</v>
       </c>
       <c r="AI9" s="0">
-        <v>26.7040493307804</v>
+        <v>29.701875523475898</v>
       </c>
       <c r="AJ9" s="0">
-        <v>61.408098661560899</v>
+        <v>67.403751046951797</v>
       </c>
       <c r="AK9" s="0">
-        <v>68.892902705192398</v>
+        <v>74.888555090583395</v>
       </c>
       <c r="AL9" s="0">
         <v>1</v>
@@ -1267,109 +1267,109 @@
         <v>19.367260063432202</v>
       </c>
       <c r="C10" s="0">
-        <v>42.734520126864503</v>
+        <v>42.734520126864403</v>
       </c>
       <c r="D10" s="0">
         <v>46.476922148680202</v>
       </c>
       <c r="E10" s="0">
-        <v>27.1713564648493</v>
+        <v>27.171358064847499</v>
       </c>
       <c r="F10" s="0">
-        <v>60.3427129296986</v>
+        <v>60.342716129695098</v>
       </c>
       <c r="G10" s="0">
-        <v>65.956315962422295</v>
+        <v>65.956319162418694</v>
       </c>
       <c r="H10" s="0">
-        <v>19.3672996631404</v>
+        <v>19.367260063467501</v>
       </c>
       <c r="I10" s="0">
-        <v>44.734599326280801</v>
+        <v>44.734520126935003</v>
       </c>
       <c r="J10" s="0">
-        <v>50.348202359004503</v>
+        <v>50.348123159658698</v>
       </c>
       <c r="K10" s="0">
-        <v>27.171356144855</v>
+        <v>27.171364064843399</v>
       </c>
       <c r="L10" s="0">
-        <v>62.342712289710001</v>
+        <v>62.342728129686797</v>
       </c>
       <c r="M10" s="0">
-        <v>69.827516333341606</v>
+        <v>69.827532173318303</v>
       </c>
       <c r="N10" s="0">
-        <v>12.5627194194797</v>
+        <v>19.367261663432402</v>
       </c>
       <c r="O10" s="0">
-        <v>29.1254388389595</v>
+        <v>42.734523326864803</v>
       </c>
       <c r="P10" s="0">
-        <v>32.867840860775303</v>
+        <v>46.476925348680602</v>
       </c>
       <c r="Q10" s="0">
-        <v>23.580184659948301</v>
+        <v>27.171358064849699</v>
       </c>
       <c r="R10" s="0">
-        <v>53.160369319896603</v>
+        <v>60.342716129699298</v>
       </c>
       <c r="S10" s="0">
-        <v>58.773972352620298</v>
+        <v>65.956319162423</v>
       </c>
       <c r="T10" s="0">
-        <v>16.9042433716433</v>
+        <v>19.3672616860418</v>
       </c>
       <c r="U10" s="0">
-        <v>39.808486743286601</v>
+        <v>44.7345233720837</v>
       </c>
       <c r="V10" s="0">
-        <v>45.422089776010203</v>
+        <v>50.348126404807303</v>
       </c>
       <c r="W10" s="0">
-        <v>23.580184659950501</v>
+        <v>27.171356464848301</v>
       </c>
       <c r="X10" s="0">
-        <v>55.160369319901001</v>
+        <v>62.342712929696603</v>
       </c>
       <c r="Y10" s="0">
-        <v>62.645173363532599</v>
+        <v>69.827516973328102</v>
       </c>
       <c r="Z10" s="0">
-        <v>14.440633572979101</v>
+        <v>19.367260063439701</v>
       </c>
       <c r="AA10" s="0">
-        <v>32.881267145958198</v>
+        <v>42.734520126879303</v>
       </c>
       <c r="AB10" s="0">
-        <v>36.623669167773997</v>
+        <v>46.476922148695103</v>
       </c>
       <c r="AC10" s="0">
-        <v>23.8655713462569</v>
+        <v>27.171356464850899</v>
       </c>
       <c r="AD10" s="0">
-        <v>53.7311426925137</v>
+        <v>60.342712929701797</v>
       </c>
       <c r="AE10" s="0">
-        <v>59.344745725237402</v>
+        <v>65.956315962425407</v>
       </c>
       <c r="AF10" s="0">
-        <v>17.192469436347299</v>
+        <v>19.367261663431801</v>
       </c>
       <c r="AG10" s="0">
-        <v>40.384938872694498</v>
+        <v>44.734523326863602</v>
       </c>
       <c r="AH10" s="0">
-        <v>45.9985419054182</v>
+        <v>50.348126359587297</v>
       </c>
       <c r="AI10" s="0">
-        <v>23.8655713453836</v>
+        <v>27.171358088345801</v>
       </c>
       <c r="AJ10" s="0">
-        <v>55.7311426907672</v>
+        <v>62.342716176691503</v>
       </c>
       <c r="AK10" s="0">
-        <v>63.215946734398798</v>
+        <v>69.827520220323095</v>
       </c>
       <c r="AL10" s="0">
         <v>1</v>
@@ -1380,112 +1380,112 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>7.6412942423850101</v>
+        <v>7.6412942423849604</v>
       </c>
       <c r="C11" s="0">
-        <v>19.282588484769999</v>
+        <v>19.282588484769899</v>
       </c>
       <c r="D11" s="0">
-        <v>23.024990506585802</v>
+        <v>23.024990506585699</v>
       </c>
       <c r="E11" s="0">
-        <v>19.6529123327077</v>
+        <v>19.6529123327247</v>
       </c>
       <c r="F11" s="0">
-        <v>45.3058246654154</v>
+        <v>45.3058246654493</v>
       </c>
       <c r="G11" s="0">
-        <v>50.919427698139103</v>
+        <v>50.919427698173003</v>
       </c>
       <c r="H11" s="0">
-        <v>8.5625792439799593</v>
+        <v>8.5625792435536603</v>
       </c>
       <c r="I11" s="0">
-        <v>23.125158487959901</v>
+        <v>23.125158487107299</v>
       </c>
       <c r="J11" s="0">
-        <v>28.7387615206836</v>
+        <v>28.738761519831002</v>
       </c>
       <c r="K11" s="0">
-        <v>19.652912332707999</v>
+        <v>19.652912332708599</v>
       </c>
       <c r="L11" s="0">
-        <v>47.305824665415898</v>
+        <v>47.305824665417198</v>
       </c>
       <c r="M11" s="0">
-        <v>54.790628709047503</v>
+        <v>54.790628709048796</v>
       </c>
       <c r="N11" s="0">
-        <v>8.7725179104659095</v>
+        <v>8.7725179102253197</v>
       </c>
       <c r="O11" s="0">
-        <v>21.545035820931801</v>
+        <v>21.5450358204506</v>
       </c>
       <c r="P11" s="0">
-        <v>25.2874378427476</v>
+        <v>25.287437842266399</v>
       </c>
       <c r="Q11" s="0">
-        <v>20.4365227590838</v>
+        <v>20.436522758849801</v>
       </c>
       <c r="R11" s="0">
-        <v>46.873045518167501</v>
+        <v>46.873045517699602</v>
       </c>
       <c r="S11" s="0">
-        <v>52.486648550891204</v>
+        <v>52.486648550423297</v>
       </c>
       <c r="T11" s="0">
-        <v>9.35622408795955</v>
+        <v>9.3562240879498209</v>
       </c>
       <c r="U11" s="0">
-        <v>24.7124481759191</v>
+        <v>24.712448175899599</v>
       </c>
       <c r="V11" s="0">
-        <v>30.326051208642799</v>
+        <v>30.326051208623301</v>
       </c>
       <c r="W11" s="0">
-        <v>20.436522758968099</v>
+        <v>20.436522758849801</v>
       </c>
       <c r="X11" s="0">
-        <v>48.873045517936198</v>
+        <v>48.873045517699602</v>
       </c>
       <c r="Y11" s="0">
-        <v>56.357849561567797</v>
+        <v>56.3578495613312</v>
       </c>
       <c r="Z11" s="0">
-        <v>8.9804280387629198</v>
+        <v>8.9804280385975197</v>
       </c>
       <c r="AA11" s="0">
-        <v>21.960856077525801</v>
+        <v>21.960856077195</v>
       </c>
       <c r="AB11" s="0">
-        <v>25.7032580993416</v>
+        <v>25.703258099010799</v>
       </c>
       <c r="AC11" s="0">
-        <v>20.6482622465664</v>
+        <v>20.648262246488599</v>
       </c>
       <c r="AD11" s="0">
-        <v>47.2965244931328</v>
+        <v>47.296524492977198</v>
       </c>
       <c r="AE11" s="0">
-        <v>52.910127525856403</v>
+        <v>52.910127525700901</v>
       </c>
       <c r="AF11" s="0">
-        <v>9.5586895145439108</v>
+        <v>9.5586895145326594</v>
       </c>
       <c r="AG11" s="0">
-        <v>25.1173790290878</v>
+        <v>25.117379029065301</v>
       </c>
       <c r="AH11" s="0">
-        <v>30.730982061811499</v>
+        <v>30.730982061789</v>
       </c>
       <c r="AI11" s="0">
-        <v>20.6482622465434</v>
+        <v>20.648262246488599</v>
       </c>
       <c r="AJ11" s="0">
-        <v>49.2965244930867</v>
+        <v>49.296524492977198</v>
       </c>
       <c r="AK11" s="0">
-        <v>56.781328536718298</v>
+        <v>56.781328536608697</v>
       </c>
       <c r="AL11" s="0">
         <v>1</v>
@@ -1514,94 +1514,94 @@
         <v>60.131309251453999</v>
       </c>
       <c r="H12" s="0">
-        <v>25.0006032517697</v>
+        <v>25.0006032517698</v>
       </c>
       <c r="I12" s="0">
-        <v>56.0012065035394</v>
+        <v>56.0012065035395</v>
       </c>
       <c r="J12" s="0">
-        <v>61.614809536263103</v>
+        <v>61.614809536263202</v>
       </c>
       <c r="K12" s="0">
         <v>24.258853109365202</v>
       </c>
       <c r="L12" s="0">
-        <v>56.517706218730297</v>
+        <v>56.517706218730403</v>
       </c>
       <c r="M12" s="0">
         <v>64.002510262361895</v>
       </c>
       <c r="N12" s="0">
-        <v>24.147032857499699</v>
+        <v>24.1470328559028</v>
       </c>
       <c r="O12" s="0">
-        <v>52.294065714999398</v>
+        <v>52.294065711805601</v>
       </c>
       <c r="P12" s="0">
-        <v>56.036467736815098</v>
+        <v>56.0364677336214</v>
       </c>
       <c r="Q12" s="0">
-        <v>25.086299932039299</v>
+        <v>25.086299930961498</v>
       </c>
       <c r="R12" s="0">
-        <v>56.172599864078599</v>
+        <v>56.172599861922897</v>
       </c>
       <c r="S12" s="0">
-        <v>61.786202896802301</v>
+        <v>61.7862028946466</v>
       </c>
       <c r="T12" s="0">
-        <v>25.0000492034224</v>
+        <v>25.067018024152901</v>
       </c>
       <c r="U12" s="0">
-        <v>56.000098406844799</v>
+        <v>56.134036048305802</v>
       </c>
       <c r="V12" s="0">
-        <v>61.613701439568402</v>
+        <v>61.747639081029398</v>
       </c>
       <c r="W12" s="0">
-        <v>25.086299931150201</v>
+        <v>25.0862999309613</v>
       </c>
       <c r="X12" s="0">
-        <v>58.172599862300402</v>
+        <v>58.1725998619225</v>
       </c>
       <c r="Y12" s="0">
-        <v>65.657403905931901</v>
+        <v>65.657403905554105</v>
       </c>
       <c r="Z12" s="0">
-        <v>23.5320832002242</v>
+        <v>23.532083198692</v>
       </c>
       <c r="AA12" s="0">
-        <v>51.0641664004484</v>
+        <v>51.064166397384</v>
       </c>
       <c r="AB12" s="0">
-        <v>54.806568422264199</v>
+        <v>54.806568419199799</v>
       </c>
       <c r="AC12" s="0">
-        <v>25.011795660953702</v>
+        <v>25.0117956607431</v>
       </c>
       <c r="AD12" s="0">
-        <v>56.023591321907404</v>
+        <v>56.0235913214863</v>
       </c>
       <c r="AE12" s="0">
-        <v>61.637194354631099</v>
+        <v>61.637194354209903</v>
       </c>
       <c r="AF12" s="0">
-        <v>24.855202184390102</v>
+        <v>25.0670180272907</v>
       </c>
       <c r="AG12" s="0">
-        <v>55.710404368780303</v>
+        <v>56.134036054581401</v>
       </c>
       <c r="AH12" s="0">
-        <v>61.324007401503998</v>
+        <v>61.747639087304997</v>
       </c>
       <c r="AI12" s="0">
-        <v>25.011795660968101</v>
+        <v>25.0117956607431</v>
       </c>
       <c r="AJ12" s="0">
-        <v>58.023591321936202</v>
+        <v>58.0235913214863</v>
       </c>
       <c r="AK12" s="0">
-        <v>65.508395365567694</v>
+        <v>65.508395365117806</v>
       </c>
       <c r="AL12" s="0">
         <v>1</v>
@@ -1612,112 +1612,112 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C13" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D13" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E13" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F13" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G13" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H13" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I13" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J13" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K13" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L13" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M13" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N13" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O13" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P13" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q13" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R13" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S13" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T13" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U13" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V13" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W13" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X13" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y13" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z13" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA13" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB13" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC13" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD13" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE13" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF13" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG13" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH13" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI13" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ13" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK13" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL13" s="0">
         <v>1</v>
@@ -1728,112 +1728,112 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C14" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D14" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E14" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F14" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G14" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H14" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I14" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J14" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K14" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L14" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M14" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N14" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O14" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P14" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q14" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R14" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S14" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T14" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U14" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V14" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W14" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X14" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y14" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z14" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA14" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB14" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC14" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD14" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE14" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF14" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG14" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH14" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI14" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ14" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK14" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL14" s="0">
         <v>1</v>
@@ -1844,112 +1844,112 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C15" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D15" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E15" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F15" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G15" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H15" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I15" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J15" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K15" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L15" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M15" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N15" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O15" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P15" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q15" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R15" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S15" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T15" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U15" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V15" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W15" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X15" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y15" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z15" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA15" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB15" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC15" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD15" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE15" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF15" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG15" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH15" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI15" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ15" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK15" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL15" s="0">
         <v>1</v>
@@ -1960,112 +1960,112 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>30.674842322007098</v>
+        <v>30.6748422969792</v>
       </c>
       <c r="C16" s="0">
-        <v>65.349684644014204</v>
+        <v>65.3496845939585</v>
       </c>
       <c r="D16" s="0">
-        <v>69.092086665829996</v>
+        <v>69.092086615774207</v>
       </c>
       <c r="E16" s="0">
-        <v>31.972953363141499</v>
+        <v>31.9729548819051</v>
       </c>
       <c r="F16" s="0">
-        <v>69.9459067262829</v>
+        <v>69.945909763810107</v>
       </c>
       <c r="G16" s="0">
-        <v>75.559509759006602</v>
+        <v>75.559512796533795</v>
       </c>
       <c r="H16" s="0">
-        <v>30.674842296978799</v>
+        <v>30.674843497893299</v>
       </c>
       <c r="I16" s="0">
-        <v>67.349684593957505</v>
+        <v>67.349686995786698</v>
       </c>
       <c r="J16" s="0">
-        <v>72.963287626681193</v>
+        <v>72.9632900285104</v>
       </c>
       <c r="K16" s="0">
-        <v>31.972953361928901</v>
+        <v>31.972953361928798</v>
       </c>
       <c r="L16" s="0">
-        <v>71.945906723857803</v>
+        <v>71.945906723857703</v>
       </c>
       <c r="M16" s="0">
-        <v>79.430710767489302</v>
+        <v>79.430710767489202</v>
       </c>
       <c r="N16" s="0">
-        <v>30.579078419918201</v>
+        <v>30.674842307417698</v>
       </c>
       <c r="O16" s="0">
-        <v>65.158156839836394</v>
+        <v>65.349684614835397</v>
       </c>
       <c r="P16" s="0">
-        <v>68.9005588616522</v>
+        <v>69.092086636651203</v>
       </c>
       <c r="Q16" s="0">
-        <v>31.925071544647501</v>
+        <v>31.972953681927802</v>
       </c>
       <c r="R16" s="0">
-        <v>69.850143089295003</v>
+        <v>69.945907363855596</v>
       </c>
       <c r="S16" s="0">
-        <v>75.463746122018705</v>
+        <v>75.559510396579199</v>
       </c>
       <c r="T16" s="0">
-        <v>30.6415341241125</v>
+        <v>30.674842296979101</v>
       </c>
       <c r="U16" s="0">
-        <v>67.283068248225007</v>
+        <v>67.349684593958202</v>
       </c>
       <c r="V16" s="0">
-        <v>72.896671280948595</v>
+        <v>72.963287626681904</v>
       </c>
       <c r="W16" s="0">
-        <v>31.925071542269599</v>
+        <v>31.972953681927901</v>
       </c>
       <c r="X16" s="0">
-        <v>71.850143084539297</v>
+        <v>71.945907363855895</v>
       </c>
       <c r="Y16" s="0">
-        <v>79.334947128170896</v>
+        <v>79.430711407487394</v>
       </c>
       <c r="Z16" s="0">
-        <v>30.610108072255599</v>
+        <v>30.674842307282798</v>
       </c>
       <c r="AA16" s="0">
-        <v>65.220216144511298</v>
+        <v>65.349684614565504</v>
       </c>
       <c r="AB16" s="0">
-        <v>68.962618166327104</v>
+        <v>69.092086636381296</v>
       </c>
       <c r="AC16" s="0">
-        <v>31.782773234127301</v>
+        <v>31.972953681929098</v>
       </c>
       <c r="AD16" s="0">
-        <v>69.565546468254496</v>
+        <v>69.945907363858197</v>
       </c>
       <c r="AE16" s="0">
-        <v>75.179149500978198</v>
+        <v>75.559510396581899</v>
       </c>
       <c r="AF16" s="0">
-        <v>30.590086773586201</v>
+        <v>30.674842303430299</v>
       </c>
       <c r="AG16" s="0">
-        <v>67.180173547172501</v>
+        <v>67.349684606860606</v>
       </c>
       <c r="AH16" s="0">
-        <v>72.793776579896203</v>
+        <v>72.963287639584294</v>
       </c>
       <c r="AI16" s="0">
-        <v>31.782773209886599</v>
+        <v>31.972953361982899</v>
       </c>
       <c r="AJ16" s="0">
-        <v>71.565546419773199</v>
+        <v>71.945906723965805</v>
       </c>
       <c r="AK16" s="0">
-        <v>79.050350463404797</v>
+        <v>79.430710767597404</v>
       </c>
       <c r="AL16" s="0">
         <v>1</v>
@@ -2082,106 +2082,106 @@
         <v>69.681683791908199</v>
       </c>
       <c r="D17" s="0">
-        <v>73.424085813723906</v>
+        <v>73.424085813724005</v>
       </c>
       <c r="E17" s="0">
-        <v>30.399195938107098</v>
+        <v>30.399195938107201</v>
       </c>
       <c r="F17" s="0">
-        <v>66.798391876214197</v>
+        <v>66.798391876214296</v>
       </c>
       <c r="G17" s="0">
-        <v>72.411994908937899</v>
+        <v>72.411994908937999</v>
       </c>
       <c r="H17" s="0">
-        <v>32.868769680115498</v>
+        <v>32.868769672481399</v>
       </c>
       <c r="I17" s="0">
-        <v>71.737539360230997</v>
+        <v>71.737539344962897</v>
       </c>
       <c r="J17" s="0">
-        <v>77.3511423929546</v>
+        <v>77.3511423776866</v>
       </c>
       <c r="K17" s="0">
         <v>30.399195938107098</v>
       </c>
       <c r="L17" s="0">
-        <v>68.798391876214197</v>
+        <v>68.798391876214296</v>
       </c>
       <c r="M17" s="0">
         <v>76.283195919845795</v>
       </c>
       <c r="N17" s="0">
-        <v>32.824319103323802</v>
+        <v>32.868769697927199</v>
       </c>
       <c r="O17" s="0">
-        <v>69.648638206647604</v>
+        <v>69.737539395854398</v>
       </c>
       <c r="P17" s="0">
-        <v>73.391040228463396</v>
+        <v>73.479941417670105</v>
       </c>
       <c r="Q17" s="0">
-        <v>30.276639920874601</v>
+        <v>30.276639920091299</v>
       </c>
       <c r="R17" s="0">
-        <v>66.553279841749202</v>
+        <v>66.553279840182697</v>
       </c>
       <c r="S17" s="0">
-        <v>72.166882874472805</v>
+        <v>72.166882872906399</v>
       </c>
       <c r="T17" s="0">
-        <v>32.626921016877098</v>
+        <v>32.868769672481299</v>
       </c>
       <c r="U17" s="0">
-        <v>71.253842033754296</v>
+        <v>71.737539344962499</v>
       </c>
       <c r="V17" s="0">
-        <v>76.867445066477899</v>
+        <v>77.351142377686202</v>
       </c>
       <c r="W17" s="0">
-        <v>30.276639923114899</v>
+        <v>30.276639920091402</v>
       </c>
       <c r="X17" s="0">
-        <v>68.553279846229898</v>
+        <v>68.553279840182697</v>
       </c>
       <c r="Y17" s="0">
-        <v>76.038083889861397</v>
+        <v>76.038083883814295</v>
       </c>
       <c r="Z17" s="0">
-        <v>32.866972306178901</v>
+        <v>32.868769288481701</v>
       </c>
       <c r="AA17" s="0">
-        <v>69.733944612357803</v>
+        <v>69.737538576963402</v>
       </c>
       <c r="AB17" s="0">
-        <v>73.476346634173595</v>
+        <v>73.479940598779194</v>
       </c>
       <c r="AC17" s="0">
-        <v>30.3096633259009</v>
+        <v>30.309663325312599</v>
       </c>
       <c r="AD17" s="0">
-        <v>66.619326651801899</v>
+        <v>66.619326650625197</v>
       </c>
       <c r="AE17" s="0">
-        <v>72.232929684525601</v>
+        <v>72.2329296833489</v>
       </c>
       <c r="AF17" s="0">
-        <v>32.204176768133799</v>
+        <v>32.8687693524789</v>
       </c>
       <c r="AG17" s="0">
-        <v>70.408353536267597</v>
+        <v>71.737538704957799</v>
       </c>
       <c r="AH17" s="0">
-        <v>76.0219565689912</v>
+        <v>77.351141737681502</v>
       </c>
       <c r="AI17" s="0">
-        <v>30.309663325332298</v>
+        <v>30.309663325312499</v>
       </c>
       <c r="AJ17" s="0">
-        <v>68.619326650664505</v>
+        <v>68.619326650624899</v>
       </c>
       <c r="AK17" s="0">
-        <v>76.104130694296103</v>
+        <v>76.104130694256497</v>
       </c>
       <c r="AL17" s="0">
         <v>0</v>
@@ -2192,112 +2192,112 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C18" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D18" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E18" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F18" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G18" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H18" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I18" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J18" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K18" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L18" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M18" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N18" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O18" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P18" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q18" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R18" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S18" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T18" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U18" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V18" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W18" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X18" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y18" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z18" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA18" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB18" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC18" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD18" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE18" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF18" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG18" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH18" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI18" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ18" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK18" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL18" s="0">
         <v>0</v>
@@ -2308,112 +2308,112 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>28.147033934561499</v>
+        <v>28.1470339345613</v>
       </c>
       <c r="C19" s="0">
-        <v>60.294067869123097</v>
+        <v>60.2940678691226</v>
       </c>
       <c r="D19" s="0">
-        <v>64.036469890938804</v>
+        <v>64.036469890938406</v>
       </c>
       <c r="E19" s="0">
+        <v>31.784882083943302</v>
+      </c>
+      <c r="F19" s="0">
+        <v>69.569764167886504</v>
+      </c>
+      <c r="G19" s="0">
+        <v>75.183367200610206</v>
+      </c>
+      <c r="H19" s="0">
+        <v>31.587082267437999</v>
+      </c>
+      <c r="I19" s="0">
+        <v>69.174164534876098</v>
+      </c>
+      <c r="J19" s="0">
+        <v>74.787767567599701</v>
+      </c>
+      <c r="K19" s="0">
         <v>31.784882083943099</v>
       </c>
-      <c r="F19" s="0">
-        <v>69.569764167886106</v>
-      </c>
-      <c r="G19" s="0">
-        <v>75.183367200609794</v>
-      </c>
-      <c r="H19" s="0">
-        <v>31.587082267438799</v>
-      </c>
-      <c r="I19" s="0">
-        <v>69.174164534877505</v>
-      </c>
-      <c r="J19" s="0">
-        <v>74.787767567601193</v>
-      </c>
-      <c r="K19" s="0">
-        <v>31.784882083943199</v>
-      </c>
       <c r="L19" s="0">
-        <v>71.569764167886305</v>
+        <v>71.569764167886106</v>
       </c>
       <c r="M19" s="0">
-        <v>79.054568211517903</v>
+        <v>79.054568211517704</v>
       </c>
       <c r="N19" s="0">
-        <v>27.616731253110199</v>
+        <v>27.616731249839798</v>
       </c>
       <c r="O19" s="0">
-        <v>59.233462506220498</v>
+        <v>59.233462499679597</v>
       </c>
       <c r="P19" s="0">
-        <v>62.975864528036297</v>
+        <v>62.975864521495403</v>
       </c>
       <c r="Q19" s="0">
-        <v>31.672994754672899</v>
+        <v>31.672994747833201</v>
       </c>
       <c r="R19" s="0">
-        <v>69.345989509345699</v>
+        <v>69.345989495666402</v>
       </c>
       <c r="S19" s="0">
-        <v>74.959592542069402</v>
+        <v>74.959592528390104</v>
       </c>
       <c r="T19" s="0">
-        <v>31.568181490629499</v>
+        <v>31.568181490474601</v>
       </c>
       <c r="U19" s="0">
-        <v>69.136362981258898</v>
+        <v>69.136362980949102</v>
       </c>
       <c r="V19" s="0">
-        <v>74.749966013982601</v>
+        <v>74.749966013672804</v>
       </c>
       <c r="W19" s="0">
-        <v>31.672994750140202</v>
+        <v>31.6729947478333</v>
       </c>
       <c r="X19" s="0">
-        <v>71.345989500280396</v>
+        <v>71.345989495666601</v>
       </c>
       <c r="Y19" s="0">
-        <v>78.830793543911994</v>
+        <v>78.830793539298199</v>
       </c>
       <c r="Z19" s="0">
-        <v>27.489989545823001</v>
+        <v>27.489989541809098</v>
       </c>
       <c r="AA19" s="0">
-        <v>58.979979091646001</v>
+        <v>58.979979083618197</v>
       </c>
       <c r="AB19" s="0">
-        <v>62.7223811134618</v>
+        <v>62.722381105434003</v>
       </c>
       <c r="AC19" s="0">
-        <v>31.9382049685893</v>
+        <v>31.938204968492499</v>
       </c>
       <c r="AD19" s="0">
-        <v>69.876409937178593</v>
+        <v>69.876409936985098</v>
       </c>
       <c r="AE19" s="0">
-        <v>75.490012969902295</v>
+        <v>75.490012969708701</v>
       </c>
       <c r="AF19" s="0">
-        <v>31.575541348399501</v>
+        <v>31.632864319101699</v>
       </c>
       <c r="AG19" s="0">
-        <v>69.151082696798994</v>
+        <v>69.265728638203399</v>
       </c>
       <c r="AH19" s="0">
-        <v>74.764685729522697</v>
+        <v>74.879331670927002</v>
       </c>
       <c r="AI19" s="0">
-        <v>31.9382049690016</v>
+        <v>31.938204968493899</v>
       </c>
       <c r="AJ19" s="0">
-        <v>71.876409938003107</v>
+        <v>71.876409936987898</v>
       </c>
       <c r="AK19" s="0">
-        <v>79.361213981634705</v>
+        <v>79.361213980619496</v>
       </c>
       <c r="AL19" s="0">
         <v>0</v>
@@ -2424,112 +2424,112 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>31.632864319103899</v>
+        <v>31.6328643191037</v>
       </c>
       <c r="C20" s="0">
-        <v>67.265728638207804</v>
+        <v>67.265728638207406</v>
       </c>
       <c r="D20" s="0">
-        <v>71.008130660023596</v>
+        <v>71.008130660023198</v>
       </c>
       <c r="E20" s="0">
-        <v>31.9729552819283</v>
+        <v>31.972953681936399</v>
       </c>
       <c r="F20" s="0">
-        <v>69.9459105638566</v>
+        <v>69.945907363872905</v>
       </c>
       <c r="G20" s="0">
-        <v>75.559513596580302</v>
+        <v>75.559510396596593</v>
       </c>
       <c r="H20" s="0">
-        <v>31.632864319124199</v>
+        <v>31.632863939107601</v>
       </c>
       <c r="I20" s="0">
-        <v>69.265728638248504</v>
+        <v>69.265727878215202</v>
       </c>
       <c r="J20" s="0">
-        <v>74.879331670972107</v>
+        <v>74.879330910938805</v>
       </c>
       <c r="K20" s="0">
-        <v>31.9729536819295</v>
+        <v>31.972953681929599</v>
       </c>
       <c r="L20" s="0">
-        <v>71.945907363859007</v>
+        <v>71.945907363859206</v>
       </c>
       <c r="M20" s="0">
-        <v>79.430711407490506</v>
+        <v>79.430711407490705</v>
       </c>
       <c r="N20" s="0">
-        <v>30.4779970675268</v>
+        <v>31.632863939102201</v>
       </c>
       <c r="O20" s="0">
-        <v>64.955994135053501</v>
+        <v>67.265727878204402</v>
       </c>
       <c r="P20" s="0">
-        <v>68.698396156869293</v>
+        <v>71.008129900020094</v>
       </c>
       <c r="Q20" s="0">
-        <v>29.792731768733301</v>
+        <v>31.972953681930399</v>
       </c>
       <c r="R20" s="0">
-        <v>65.585463537466595</v>
+        <v>69.945907363860798</v>
       </c>
       <c r="S20" s="0">
-        <v>71.199066570190197</v>
+        <v>75.5595103965845</v>
       </c>
       <c r="T20" s="0">
-        <v>29.618112463330299</v>
+        <v>31.632864319102399</v>
       </c>
       <c r="U20" s="0">
-        <v>65.236224926660597</v>
+        <v>69.265728638204706</v>
       </c>
       <c r="V20" s="0">
-        <v>70.849827959384299</v>
+        <v>74.879331670928394</v>
       </c>
       <c r="W20" s="0">
-        <v>29.792731768799701</v>
+        <v>31.9729533019343</v>
       </c>
       <c r="X20" s="0">
-        <v>67.585463537599296</v>
+        <v>71.945906603868593</v>
       </c>
       <c r="Y20" s="0">
-        <v>75.070267581230894</v>
+        <v>79.430710647500206</v>
       </c>
       <c r="Z20" s="0">
-        <v>31.050034419403399</v>
+        <v>31.632864319114901</v>
       </c>
       <c r="AA20" s="0">
-        <v>66.100068838806905</v>
+        <v>67.265728638229803</v>
       </c>
       <c r="AB20" s="0">
-        <v>69.842470860622598</v>
+        <v>71.008130660045595</v>
       </c>
       <c r="AC20" s="0">
-        <v>31.1924091328355</v>
+        <v>31.972953681930999</v>
       </c>
       <c r="AD20" s="0">
-        <v>68.384818265671001</v>
+        <v>69.945907363862105</v>
       </c>
       <c r="AE20" s="0">
-        <v>73.998421298394703</v>
+        <v>75.559510396585793</v>
       </c>
       <c r="AF20" s="0">
-        <v>30.7390308205919</v>
+        <v>31.632864319102701</v>
       </c>
       <c r="AG20" s="0">
-        <v>67.478061641183899</v>
+        <v>69.265728638205402</v>
       </c>
       <c r="AH20" s="0">
-        <v>73.091664673907601</v>
+        <v>74.879331670929005</v>
       </c>
       <c r="AI20" s="0">
-        <v>31.192409166011402</v>
+        <v>31.972953321929001</v>
       </c>
       <c r="AJ20" s="0">
-        <v>70.384818332022803</v>
+        <v>71.945906643857896</v>
       </c>
       <c r="AK20" s="0">
-        <v>77.869622375654401</v>
+        <v>79.430710687489494</v>
       </c>
       <c r="AL20" s="0">
         <v>0</v>
@@ -2540,112 +2540,112 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>29.4632986813656</v>
+        <v>29.463298681424099</v>
       </c>
       <c r="C21" s="0">
-        <v>62.926597362731101</v>
+        <v>62.926597362848298</v>
       </c>
       <c r="D21" s="0">
-        <v>66.668999384546893</v>
+        <v>66.668999384664104</v>
       </c>
       <c r="E21" s="0">
-        <v>28.577257382152901</v>
+        <v>28.577257381719299</v>
       </c>
       <c r="F21" s="0">
-        <v>63.154514764305802</v>
+        <v>63.154514763438499</v>
       </c>
       <c r="G21" s="0">
-        <v>68.768117797029404</v>
+        <v>68.768117796162201</v>
       </c>
       <c r="H21" s="0">
-        <v>29.463298301366098</v>
+        <v>29.463300281363001</v>
       </c>
       <c r="I21" s="0">
-        <v>64.926596602732204</v>
+        <v>64.926600562725994</v>
       </c>
       <c r="J21" s="0">
-        <v>70.540199635455906</v>
+        <v>70.540203595449697</v>
       </c>
       <c r="K21" s="0">
-        <v>28.577257621693299</v>
+        <v>28.577258901695501</v>
       </c>
       <c r="L21" s="0">
-        <v>65.154515243386697</v>
+        <v>65.154517803390902</v>
       </c>
       <c r="M21" s="0">
-        <v>72.639319287018196</v>
+        <v>72.639321847022501</v>
       </c>
       <c r="N21" s="0">
-        <v>26.7165932581003</v>
+        <v>29.463300281364798</v>
       </c>
       <c r="O21" s="0">
-        <v>57.4331865162006</v>
+        <v>62.926600562729597</v>
       </c>
       <c r="P21" s="0">
-        <v>61.175588538016399</v>
+        <v>66.669002584545396</v>
       </c>
       <c r="Q21" s="0">
-        <v>28.337969677405798</v>
+        <v>28.577257321714399</v>
       </c>
       <c r="R21" s="0">
-        <v>62.675939354811703</v>
+        <v>63.154514643428897</v>
       </c>
       <c r="S21" s="0">
-        <v>68.289542387535306</v>
+        <v>68.768117676152599</v>
       </c>
       <c r="T21" s="0">
-        <v>28.361719478401898</v>
+        <v>29.463298682609</v>
       </c>
       <c r="U21" s="0">
-        <v>62.723438956803697</v>
+        <v>64.926597365218001</v>
       </c>
       <c r="V21" s="0">
-        <v>68.337041989527407</v>
+        <v>70.540200397941604</v>
       </c>
       <c r="W21" s="0">
-        <v>28.337969678658801</v>
+        <v>28.577257321714701</v>
       </c>
       <c r="X21" s="0">
-        <v>64.675939357317603</v>
+        <v>65.154514643429295</v>
       </c>
       <c r="Y21" s="0">
-        <v>72.160743400949201</v>
+        <v>72.639318687060893</v>
       </c>
       <c r="Z21" s="0">
-        <v>28.937069199099401</v>
+        <v>29.463298681369</v>
       </c>
       <c r="AA21" s="0">
-        <v>61.874138398198802</v>
+        <v>62.926597362738001</v>
       </c>
       <c r="AB21" s="0">
-        <v>65.616540420014502</v>
+        <v>66.6689993845537</v>
       </c>
       <c r="AC21" s="0">
-        <v>28.4965518811069</v>
+        <v>28.577258901693899</v>
       </c>
       <c r="AD21" s="0">
-        <v>62.9931037622137</v>
+        <v>63.154517803387698</v>
       </c>
       <c r="AE21" s="0">
-        <v>68.606706794937395</v>
+        <v>68.768120836111393</v>
       </c>
       <c r="AF21" s="0">
-        <v>28.5773182073032</v>
+        <v>29.463298301368599</v>
       </c>
       <c r="AG21" s="0">
-        <v>63.154636414606301</v>
+        <v>64.926596602737106</v>
       </c>
       <c r="AH21" s="0">
-        <v>68.768239447330004</v>
+        <v>70.540199635460795</v>
       </c>
       <c r="AI21" s="0">
-        <v>28.496551881614799</v>
+        <v>28.5772573816994</v>
       </c>
       <c r="AJ21" s="0">
-        <v>64.993103763229598</v>
+        <v>65.154514763398794</v>
       </c>
       <c r="AK21" s="0">
-        <v>72.477907806861097</v>
+        <v>72.639318807030406</v>
       </c>
       <c r="AL21" s="0">
         <v>0</v>
@@ -2656,112 +2656,112 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>31.183977711299299</v>
+        <v>31.183977711300301</v>
       </c>
       <c r="C22" s="0">
-        <v>66.367955422598598</v>
+        <v>66.367955422600602</v>
       </c>
       <c r="D22" s="0">
-        <v>70.110357444414404</v>
+        <v>70.110357444416394</v>
       </c>
       <c r="E22" s="0">
-        <v>29.7018759034795</v>
+        <v>29.701875583479801</v>
       </c>
       <c r="F22" s="0">
-        <v>65.403751806959093</v>
+        <v>65.403751166959594</v>
       </c>
       <c r="G22" s="0">
-        <v>71.017354839682795</v>
+        <v>71.017354199683297</v>
       </c>
       <c r="H22" s="0">
-        <v>31.183977711337999</v>
+        <v>31.183977711335</v>
       </c>
       <c r="I22" s="0">
-        <v>68.367955422676104</v>
+        <v>68.367955422669993</v>
       </c>
       <c r="J22" s="0">
-        <v>73.981558455399707</v>
+        <v>73.981558455393696</v>
       </c>
       <c r="K22" s="0">
-        <v>29.7018759034816</v>
+        <v>29.7018755835946</v>
       </c>
       <c r="L22" s="0">
-        <v>67.403751806963299</v>
+        <v>67.4037511671891</v>
       </c>
       <c r="M22" s="0">
-        <v>74.888555850594798</v>
+        <v>74.888555210820698</v>
       </c>
       <c r="N22" s="0">
-        <v>30.142242072477899</v>
+        <v>31.183977711331899</v>
       </c>
       <c r="O22" s="0">
-        <v>64.284484144955798</v>
+        <v>66.367955422663798</v>
       </c>
       <c r="P22" s="0">
-        <v>68.026886166771604</v>
+        <v>70.110357444479604</v>
       </c>
       <c r="Q22" s="0">
-        <v>28.852099999857799</v>
+        <v>29.701875903563199</v>
       </c>
       <c r="R22" s="0">
-        <v>63.704199999715598</v>
+        <v>65.403751807126497</v>
       </c>
       <c r="S22" s="0">
-        <v>69.317803032439301</v>
+        <v>71.017354839850199</v>
       </c>
       <c r="T22" s="0">
-        <v>29.032152575733399</v>
+        <v>31.183977711321599</v>
       </c>
       <c r="U22" s="0">
-        <v>64.064305151466897</v>
+        <v>68.367955422643206</v>
       </c>
       <c r="V22" s="0">
-        <v>69.6779081841905</v>
+        <v>73.981558455366894</v>
       </c>
       <c r="W22" s="0">
-        <v>28.852100000486502</v>
+        <v>29.701875903491</v>
       </c>
       <c r="X22" s="0">
-        <v>65.704200000973103</v>
+        <v>67.403751806982001</v>
       </c>
       <c r="Y22" s="0">
-        <v>73.189004044604602</v>
+        <v>74.8885558506135</v>
       </c>
       <c r="Z22" s="0">
-        <v>30.401331596928902</v>
+        <v>31.1839777113092</v>
       </c>
       <c r="AA22" s="0">
-        <v>64.802663193857896</v>
+        <v>66.367955422618394</v>
       </c>
       <c r="AB22" s="0">
-        <v>68.545065215673603</v>
+        <v>70.1103574444342</v>
       </c>
       <c r="AC22" s="0">
-        <v>28.5673171582769</v>
+        <v>29.701875523483999</v>
       </c>
       <c r="AD22" s="0">
-        <v>63.134634316553701</v>
+        <v>65.403751046967997</v>
       </c>
       <c r="AE22" s="0">
-        <v>68.748237349277403</v>
+        <v>71.0173540796917</v>
       </c>
       <c r="AF22" s="0">
-        <v>28.798625286908202</v>
+        <v>31.183977711262699</v>
       </c>
       <c r="AG22" s="0">
-        <v>63.597250573816403</v>
+        <v>68.367955422525398</v>
       </c>
       <c r="AH22" s="0">
-        <v>69.210853606540098</v>
+        <v>73.9815584552491</v>
       </c>
       <c r="AI22" s="0">
-        <v>28.567317153845501</v>
+        <v>29.701875903479898</v>
       </c>
       <c r="AJ22" s="0">
-        <v>65.134634307691002</v>
+        <v>67.403751806959704</v>
       </c>
       <c r="AK22" s="0">
-        <v>72.619438351322501</v>
+        <v>74.888555850591302</v>
       </c>
       <c r="AL22" s="0">
         <v>0</v>
@@ -2772,112 +2772,112 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>11.090362975678801</v>
+        <v>11.090365454839199</v>
       </c>
       <c r="C23" s="0">
-        <v>26.180725951357601</v>
+        <v>26.180730909678498</v>
       </c>
       <c r="D23" s="0">
-        <v>29.923127973173401</v>
+        <v>29.923132931494301</v>
       </c>
       <c r="E23" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F23" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G23" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H23" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I23" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J23" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K23" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L23" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M23" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N23" s="0">
-        <v>3.9408358669711299</v>
+        <v>11.090362977654801</v>
       </c>
       <c r="O23" s="0">
-        <v>11.8816717339423</v>
+        <v>26.180725955309601</v>
       </c>
       <c r="P23" s="0">
-        <v>15.624073755758101</v>
+        <v>29.9231279771254</v>
       </c>
       <c r="Q23" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R23" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S23" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T23" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U23" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V23" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W23" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X23" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y23" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z23" s="0">
-        <v>-0</v>
+        <v>11.0903629756318</v>
       </c>
       <c r="AA23" s="0">
-        <v>4</v>
+        <v>26.1807259512637</v>
       </c>
       <c r="AB23" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127973079399</v>
       </c>
       <c r="AC23" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD23" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE23" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF23" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG23" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH23" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI23" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ23" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK23" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL23" s="0">
         <v>0</v>
@@ -2888,112 +2888,112 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>30.102485829285101</v>
+        <v>30.102486149359802</v>
       </c>
       <c r="C24" s="0">
-        <v>64.204971658570102</v>
+        <v>64.204972298719596</v>
       </c>
       <c r="D24" s="0">
-        <v>67.947373680385894</v>
+        <v>67.947374320535403</v>
       </c>
       <c r="E24" s="0">
-        <v>28.577257381699599</v>
+        <v>28.5772577016984</v>
       </c>
       <c r="F24" s="0">
-        <v>63.154514763399199</v>
+        <v>63.1545154033969</v>
       </c>
       <c r="G24" s="0">
-        <v>68.768117796122894</v>
+        <v>68.768118436120503</v>
       </c>
       <c r="H24" s="0">
-        <v>30.102487749151098</v>
+        <v>30.102487749152601</v>
       </c>
       <c r="I24" s="0">
-        <v>66.204975498302204</v>
+        <v>66.204975498305103</v>
       </c>
       <c r="J24" s="0">
-        <v>71.818578531025906</v>
+        <v>71.818578531028805</v>
       </c>
       <c r="K24" s="0">
-        <v>28.577258902033801</v>
+        <v>28.5772573816994</v>
       </c>
       <c r="L24" s="0">
-        <v>65.154517804067694</v>
+        <v>65.154514763398794</v>
       </c>
       <c r="M24" s="0">
-        <v>72.639321847699307</v>
+        <v>72.639318807030406</v>
       </c>
       <c r="N24" s="0">
-        <v>29.273982408892302</v>
+        <v>30.102486149196</v>
       </c>
       <c r="O24" s="0">
-        <v>62.547964817784496</v>
+        <v>64.204972298391993</v>
       </c>
       <c r="P24" s="0">
-        <v>66.290366839600296</v>
+        <v>67.9473743202078</v>
       </c>
       <c r="Q24" s="0">
-        <v>28.4723411494973</v>
+        <v>28.5772593016885</v>
       </c>
       <c r="R24" s="0">
-        <v>62.944682298994699</v>
+        <v>63.154518603377099</v>
       </c>
       <c r="S24" s="0">
-        <v>68.558285331718395</v>
+        <v>68.768121636100702</v>
       </c>
       <c r="T24" s="0">
-        <v>29.0902743346325</v>
+        <v>30.102487749151699</v>
       </c>
       <c r="U24" s="0">
-        <v>64.180548669265093</v>
+        <v>66.204975498303398</v>
       </c>
       <c r="V24" s="0">
-        <v>69.794151701988795</v>
+        <v>71.818578531027001</v>
       </c>
       <c r="W24" s="0">
-        <v>28.472341151087999</v>
+        <v>28.577257713754999</v>
       </c>
       <c r="X24" s="0">
-        <v>64.944682302176005</v>
+        <v>65.154515427510006</v>
       </c>
       <c r="Y24" s="0">
-        <v>72.429486345807604</v>
+        <v>72.639319471141604</v>
       </c>
       <c r="Z24" s="0">
-        <v>30.069576111122601</v>
+        <v>30.102486149152501</v>
       </c>
       <c r="AA24" s="0">
-        <v>64.139152222245301</v>
+        <v>64.204972298304995</v>
       </c>
       <c r="AB24" s="0">
-        <v>67.881554244060993</v>
+        <v>67.947374320120801</v>
       </c>
       <c r="AC24" s="0">
-        <v>28.456874448500699</v>
+        <v>28.577258975942399</v>
       </c>
       <c r="AD24" s="0">
-        <v>62.913748897001398</v>
+        <v>63.154517951884799</v>
       </c>
       <c r="AE24" s="0">
-        <v>68.5273519297251</v>
+        <v>68.768120984608501</v>
       </c>
       <c r="AF24" s="0">
-        <v>28.679721314797799</v>
+        <v>30.1024861487255</v>
       </c>
       <c r="AG24" s="0">
-        <v>63.359442629595598</v>
+        <v>66.204972297450894</v>
       </c>
       <c r="AH24" s="0">
-        <v>68.973045662319294</v>
+        <v>71.818575330174596</v>
       </c>
       <c r="AI24" s="0">
-        <v>28.456874448536102</v>
+        <v>28.5772576216993</v>
       </c>
       <c r="AJ24" s="0">
-        <v>64.913748897072296</v>
+        <v>65.154515243398606</v>
       </c>
       <c r="AK24" s="0">
-        <v>72.398552940703794</v>
+        <v>72.639319287030204</v>
       </c>
       <c r="AL24" s="0">
         <v>0</v>
@@ -3004,112 +3004,112 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>33.1935891235646</v>
+        <v>33.106494191049599</v>
       </c>
       <c r="C25" s="0">
-        <v>70.387178247129199</v>
+        <v>70.212988382099098</v>
       </c>
       <c r="D25" s="0">
-        <v>74.129580268945006</v>
+        <v>73.955390403914905</v>
       </c>
       <c r="E25" s="0">
+        <v>33.220994011820601</v>
+      </c>
+      <c r="F25" s="0">
+        <v>72.441988023641301</v>
+      </c>
+      <c r="G25" s="0">
+        <v>78.055591056364904</v>
+      </c>
+      <c r="H25" s="0">
+        <v>33.271065067863198</v>
+      </c>
+      <c r="I25" s="0">
+        <v>72.542130135726495</v>
+      </c>
+      <c r="J25" s="0">
+        <v>78.155733168450197</v>
+      </c>
+      <c r="K25" s="0">
         <v>33.220993631822502</v>
       </c>
-      <c r="F25" s="0">
-        <v>72.441987263645103</v>
-      </c>
-      <c r="G25" s="0">
-        <v>78.055590296368706</v>
-      </c>
-      <c r="H25" s="0">
-        <v>33.271072664992801</v>
-      </c>
-      <c r="I25" s="0">
-        <v>72.542145329985601</v>
-      </c>
-      <c r="J25" s="0">
-        <v>78.155748362709204</v>
-      </c>
-      <c r="K25" s="0">
-        <v>33.220994011819599</v>
-      </c>
       <c r="L25" s="0">
-        <v>74.441988023639098</v>
+        <v>74.441987263645004</v>
       </c>
       <c r="M25" s="0">
-        <v>81.926792067270696</v>
+        <v>81.926791307276602</v>
       </c>
       <c r="N25" s="0">
-        <v>32.615651517038501</v>
+        <v>32.997399586631403</v>
       </c>
       <c r="O25" s="0">
-        <v>69.231303034077001</v>
+        <v>69.994799173262805</v>
       </c>
       <c r="P25" s="0">
-        <v>72.973705055892793</v>
+        <v>73.737201195078498</v>
       </c>
       <c r="Q25" s="0">
-        <v>33.170845126861998</v>
+        <v>33.220994011821801</v>
       </c>
       <c r="R25" s="0">
-        <v>72.341690253723996</v>
+        <v>72.441988023643603</v>
       </c>
       <c r="S25" s="0">
-        <v>77.955293286447599</v>
+        <v>78.055591056367305</v>
       </c>
       <c r="T25" s="0">
-        <v>31.943958138254001</v>
+        <v>33.271104641630998</v>
       </c>
       <c r="U25" s="0">
-        <v>69.887916276507895</v>
+        <v>72.542209283261897</v>
       </c>
       <c r="V25" s="0">
-        <v>75.501519309231597</v>
+        <v>78.1558123159856</v>
       </c>
       <c r="W25" s="0">
-        <v>33.170845126773898</v>
+        <v>33.2209936319083</v>
       </c>
       <c r="X25" s="0">
-        <v>74.341690253547796</v>
+        <v>74.4419872638165</v>
       </c>
       <c r="Y25" s="0">
-        <v>81.826494297179394</v>
+        <v>81.926791307448099</v>
       </c>
       <c r="Z25" s="0">
-        <v>32.628459817138001</v>
+        <v>32.799470120229699</v>
       </c>
       <c r="AA25" s="0">
-        <v>69.256919634276002</v>
+        <v>69.598940240459498</v>
       </c>
       <c r="AB25" s="0">
-        <v>72.999321656091695</v>
+        <v>73.341342262275205</v>
       </c>
       <c r="AC25" s="0">
-        <v>33.205488540625602</v>
+        <v>33.220994011824601</v>
       </c>
       <c r="AD25" s="0">
-        <v>72.410977081251204</v>
+        <v>72.441988023649301</v>
       </c>
       <c r="AE25" s="0">
-        <v>78.024580113974906</v>
+        <v>78.055591056372904</v>
       </c>
       <c r="AF25" s="0">
-        <v>31.360707570383301</v>
+        <v>33.271065066877398</v>
       </c>
       <c r="AG25" s="0">
-        <v>68.721415140766695</v>
+        <v>72.542130133754796</v>
       </c>
       <c r="AH25" s="0">
-        <v>74.335018173490397</v>
+        <v>78.155733166478498</v>
       </c>
       <c r="AI25" s="0">
-        <v>33.205488541844304</v>
+        <v>33.220993631844799</v>
       </c>
       <c r="AJ25" s="0">
-        <v>74.410977083688607</v>
+        <v>74.441987263689597</v>
       </c>
       <c r="AK25" s="0">
-        <v>81.895781127320106</v>
+        <v>81.926791307321196</v>
       </c>
       <c r="AL25" s="0">
         <v>0</v>
@@ -3120,112 +3120,112 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>19.366991421148501</v>
+        <v>19.366991421155099</v>
       </c>
       <c r="C26" s="0">
-        <v>42.733982842296903</v>
+        <v>42.733982842310198</v>
       </c>
       <c r="D26" s="0">
-        <v>46.476384864112703</v>
+        <v>46.476384864125897</v>
       </c>
       <c r="E26" s="0">
-        <v>28.5772495950125</v>
+        <v>28.577249595008599</v>
       </c>
       <c r="F26" s="0">
-        <v>63.154499190025099</v>
+        <v>63.154499190017098</v>
       </c>
       <c r="G26" s="0">
-        <v>68.768102222748695</v>
+        <v>68.768102222740794</v>
       </c>
       <c r="H26" s="0">
-        <v>19.2323849157263</v>
+        <v>19.232384915726399</v>
       </c>
       <c r="I26" s="0">
-        <v>44.4647698314526</v>
+        <v>44.464769831452799</v>
       </c>
       <c r="J26" s="0">
-        <v>50.078372864176302</v>
+        <v>50.078372864176501</v>
       </c>
       <c r="K26" s="0">
-        <v>28.577249595002002</v>
+        <v>28.577249594993301</v>
       </c>
       <c r="L26" s="0">
-        <v>65.154499190004103</v>
+        <v>65.154499189986694</v>
       </c>
       <c r="M26" s="0">
-        <v>72.639303233635601</v>
+        <v>72.639303233618307</v>
       </c>
       <c r="N26" s="0">
-        <v>18.737802620360899</v>
+        <v>19.367260063435001</v>
       </c>
       <c r="O26" s="0">
-        <v>41.475605240721798</v>
+        <v>42.734520126870002</v>
       </c>
       <c r="P26" s="0">
-        <v>45.218007262537597</v>
+        <v>46.476922148685702</v>
       </c>
       <c r="Q26" s="0">
-        <v>28.1463903178735</v>
+        <v>28.5772593592914</v>
       </c>
       <c r="R26" s="0">
-        <v>62.2927806357471</v>
+        <v>63.154518718582899</v>
       </c>
       <c r="S26" s="0">
-        <v>67.906383668470696</v>
+        <v>68.768121751306495</v>
       </c>
       <c r="T26" s="0">
-        <v>19.328450356908601</v>
+        <v>19.367260063431001</v>
       </c>
       <c r="U26" s="0">
-        <v>44.656900713817102</v>
+        <v>44.734520126862101</v>
       </c>
       <c r="V26" s="0">
-        <v>50.270503746540797</v>
+        <v>50.348123159585697</v>
       </c>
       <c r="W26" s="0">
-        <v>28.146390319319501</v>
+        <v>28.5772593604846</v>
       </c>
       <c r="X26" s="0">
-        <v>64.292780638638902</v>
+        <v>65.154518720969094</v>
       </c>
       <c r="Y26" s="0">
-        <v>71.777584682270501</v>
+        <v>72.639322764600706</v>
       </c>
       <c r="Z26" s="0">
-        <v>19.343123855169399</v>
+        <v>19.367260063430599</v>
       </c>
       <c r="AA26" s="0">
-        <v>42.686247710338797</v>
+        <v>42.734520126861099</v>
       </c>
       <c r="AB26" s="0">
-        <v>46.428649732154597</v>
+        <v>46.476922148676898</v>
       </c>
       <c r="AC26" s="0">
-        <v>28.575221978833</v>
+        <v>28.575221977751902</v>
       </c>
       <c r="AD26" s="0">
-        <v>63.150443957666099</v>
+        <v>63.150443955503803</v>
       </c>
       <c r="AE26" s="0">
-        <v>68.764046990389701</v>
+        <v>68.764046988227506</v>
       </c>
       <c r="AF26" s="0">
-        <v>18.963379148857701</v>
+        <v>18.963379148104998</v>
       </c>
       <c r="AG26" s="0">
-        <v>43.926758297715402</v>
+        <v>43.926758296209897</v>
       </c>
       <c r="AH26" s="0">
-        <v>49.540361330439097</v>
+        <v>49.540361328933599</v>
       </c>
       <c r="AI26" s="0">
-        <v>28.575221978646599</v>
+        <v>28.5752219777584</v>
       </c>
       <c r="AJ26" s="0">
-        <v>65.150443957293206</v>
+        <v>65.150443955516806</v>
       </c>
       <c r="AK26" s="0">
-        <v>72.635248000924804</v>
+        <v>72.635247999148405</v>
       </c>
       <c r="AL26" s="0">
         <v>0</v>
@@ -3236,112 +3236,112 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>17.366872688780301</v>
+        <v>17.3668726887806</v>
       </c>
       <c r="C27" s="0">
-        <v>38.733745377560503</v>
+        <v>38.733745377561199</v>
       </c>
       <c r="D27" s="0">
-        <v>42.476147399376302</v>
+        <v>42.476147399376998</v>
       </c>
       <c r="E27" s="0">
-        <v>27.1713564648479</v>
+        <v>27.1713564648526</v>
       </c>
       <c r="F27" s="0">
-        <v>60.3427129296959</v>
+        <v>60.342712929705201</v>
       </c>
       <c r="G27" s="0">
-        <v>65.956315962419495</v>
+        <v>65.956315962428903</v>
       </c>
       <c r="H27" s="0">
-        <v>17.366872688805501</v>
+        <v>17.366872688799699</v>
       </c>
       <c r="I27" s="0">
-        <v>40.733745377611001</v>
+        <v>40.733745377599497</v>
       </c>
       <c r="J27" s="0">
-        <v>46.347348410334703</v>
+        <v>46.3473484103232</v>
       </c>
       <c r="K27" s="0">
-        <v>27.171356464887801</v>
+        <v>27.171356144845699</v>
       </c>
       <c r="L27" s="0">
-        <v>62.342712929775601</v>
+        <v>62.342712289691399</v>
       </c>
       <c r="M27" s="0">
-        <v>69.827516973407199</v>
+        <v>69.827516333323004</v>
       </c>
       <c r="N27" s="0">
-        <v>13.8013577410293</v>
+        <v>17.3668726887642</v>
       </c>
       <c r="O27" s="0">
-        <v>31.602715482058699</v>
+        <v>38.7337453775284</v>
       </c>
       <c r="P27" s="0">
-        <v>35.345117503874498</v>
+        <v>42.4761473993442</v>
       </c>
       <c r="Q27" s="0">
-        <v>25.043227901376</v>
+        <v>27.171356464848198</v>
       </c>
       <c r="R27" s="0">
-        <v>56.086455802752099</v>
+        <v>60.342712929696503</v>
       </c>
       <c r="S27" s="0">
-        <v>61.700058835475701</v>
+        <v>65.956315962420206</v>
       </c>
       <c r="T27" s="0">
-        <v>16.239972744300001</v>
+        <v>17.366874288748502</v>
       </c>
       <c r="U27" s="0">
-        <v>38.479945488600002</v>
+        <v>40.733748577496897</v>
       </c>
       <c r="V27" s="0">
-        <v>44.093548521323697</v>
+        <v>46.347351610220599</v>
       </c>
       <c r="W27" s="0">
-        <v>25.043227901384199</v>
+        <v>27.171356464848301</v>
       </c>
       <c r="X27" s="0">
-        <v>58.086455802768398</v>
+        <v>62.342712929696702</v>
       </c>
       <c r="Y27" s="0">
-        <v>65.571259846399997</v>
+        <v>69.827516973328201</v>
       </c>
       <c r="Z27" s="0">
-        <v>14.672093712804299</v>
+        <v>17.366872688767199</v>
       </c>
       <c r="AA27" s="0">
-        <v>33.344187425608602</v>
+        <v>38.733745377534397</v>
       </c>
       <c r="AB27" s="0">
-        <v>37.086589447424302</v>
+        <v>42.476147399350197</v>
       </c>
       <c r="AC27" s="0">
-        <v>24.967577070512998</v>
+        <v>27.171358064854399</v>
       </c>
       <c r="AD27" s="0">
-        <v>55.935154141025997</v>
+        <v>60.342716129708897</v>
       </c>
       <c r="AE27" s="0">
-        <v>61.548757173749699</v>
+        <v>65.956319162432493</v>
       </c>
       <c r="AF27" s="0">
-        <v>16.8587508750797</v>
+        <v>17.366872308755301</v>
       </c>
       <c r="AG27" s="0">
-        <v>39.717501750159499</v>
+        <v>40.733744617510503</v>
       </c>
       <c r="AH27" s="0">
-        <v>45.331104782883102</v>
+        <v>46.347347650234198</v>
       </c>
       <c r="AI27" s="0">
-        <v>24.967577082277501</v>
+        <v>27.171356464847999</v>
       </c>
       <c r="AJ27" s="0">
-        <v>57.935154164554902</v>
+        <v>62.342712929695999</v>
       </c>
       <c r="AK27" s="0">
-        <v>65.4199582081865</v>
+        <v>69.827516973327505</v>
       </c>
       <c r="AL27" s="0">
         <v>0</v>
@@ -3352,112 +3352,112 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C28" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D28" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E28" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F28" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G28" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H28" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I28" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J28" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K28" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L28" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M28" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N28" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O28" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P28" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q28" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R28" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S28" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T28" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U28" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V28" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W28" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X28" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y28" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z28" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA28" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB28" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC28" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD28" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE28" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF28" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG28" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH28" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI28" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ28" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK28" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL28" s="0">
         <v>0</v>
@@ -3468,112 +3468,112 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C29" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D29" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E29" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F29" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G29" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H29" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I29" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J29" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K29" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L29" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M29" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N29" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O29" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P29" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q29" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R29" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S29" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T29" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U29" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V29" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W29" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X29" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y29" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z29" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA29" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB29" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC29" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD29" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE29" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF29" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG29" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH29" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI29" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ29" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK29" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL29" s="0">
         <v>0</v>
@@ -3584,112 +3584,112 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>21.071647862839502</v>
+        <v>21.071647562834599</v>
       </c>
       <c r="C30" s="0">
-        <v>46.143295725679003</v>
+        <v>46.143295125669198</v>
       </c>
       <c r="D30" s="0">
-        <v>49.885697747494802</v>
+        <v>49.885697147484898</v>
       </c>
       <c r="E30" s="0">
-        <v>27.171358093665098</v>
+        <v>27.171358064848299</v>
       </c>
       <c r="F30" s="0">
-        <v>60.342716187330304</v>
+        <v>60.342716129696598</v>
       </c>
       <c r="G30" s="0">
-        <v>65.956319220053999</v>
+        <v>65.9563191624203</v>
       </c>
       <c r="H30" s="0">
-        <v>21.071647862849201</v>
+        <v>21.071687462596099</v>
       </c>
       <c r="I30" s="0">
-        <v>48.143295725698401</v>
+        <v>48.143374925192099</v>
       </c>
       <c r="J30" s="0">
-        <v>53.756898758421997</v>
+        <v>53.756977957915801</v>
       </c>
       <c r="K30" s="0">
-        <v>27.171356464877199</v>
+        <v>27.171356464876801</v>
       </c>
       <c r="L30" s="0">
-        <v>62.342712929754498</v>
+        <v>62.342712929753503</v>
       </c>
       <c r="M30" s="0">
-        <v>69.827516973385997</v>
+        <v>69.827516973385102</v>
       </c>
       <c r="N30" s="0">
-        <v>14.7434302461117</v>
+        <v>21.071649462818499</v>
       </c>
       <c r="O30" s="0">
-        <v>33.4868604922233</v>
+        <v>46.143298925636998</v>
       </c>
       <c r="P30" s="0">
-        <v>37.2292625140391</v>
+        <v>49.885700947452797</v>
       </c>
       <c r="Q30" s="0">
-        <v>22.5453899245143</v>
+        <v>27.1713580648515</v>
       </c>
       <c r="R30" s="0">
-        <v>51.0907798490286</v>
+        <v>60.3427161297029</v>
       </c>
       <c r="S30" s="0">
-        <v>56.704382881752302</v>
+        <v>65.956319162426595</v>
       </c>
       <c r="T30" s="0">
-        <v>17.4980603642021</v>
+        <v>21.071647482817198</v>
       </c>
       <c r="U30" s="0">
-        <v>40.996120728404101</v>
+        <v>48.143294965634396</v>
       </c>
       <c r="V30" s="0">
-        <v>46.609723761127803</v>
+        <v>53.756897998358099</v>
       </c>
       <c r="W30" s="0">
-        <v>22.5453899245143</v>
+        <v>27.171356084851698</v>
       </c>
       <c r="X30" s="0">
-        <v>53.0907798490286</v>
+        <v>62.342712169703397</v>
       </c>
       <c r="Y30" s="0">
-        <v>60.575583892660198</v>
+        <v>69.827516213335002</v>
       </c>
       <c r="Z30" s="0">
-        <v>18.5895050847368</v>
+        <v>21.071649469424099</v>
       </c>
       <c r="AA30" s="0">
-        <v>41.179010169473599</v>
+        <v>46.143298938848197</v>
       </c>
       <c r="AB30" s="0">
-        <v>44.921412191289399</v>
+        <v>49.885700960664003</v>
       </c>
       <c r="AC30" s="0">
-        <v>25.516023804446501</v>
+        <v>27.171356464848099</v>
       </c>
       <c r="AD30" s="0">
-        <v>57.032047608892903</v>
+        <v>60.342712929696198</v>
       </c>
       <c r="AE30" s="0">
-        <v>62.645650641616598</v>
+        <v>65.956315962419893</v>
       </c>
       <c r="AF30" s="0">
-        <v>19.879392402665001</v>
+        <v>21.071647482822598</v>
       </c>
       <c r="AG30" s="0">
-        <v>45.758784805330002</v>
+        <v>48.143294965645303</v>
       </c>
       <c r="AH30" s="0">
-        <v>51.372387838053697</v>
+        <v>53.756897998368999</v>
       </c>
       <c r="AI30" s="0">
-        <v>25.5160238064448</v>
+        <v>27.171358064849102</v>
       </c>
       <c r="AJ30" s="0">
-        <v>59.032047612889698</v>
+        <v>62.342716129698097</v>
       </c>
       <c r="AK30" s="0">
-        <v>66.516851656521197</v>
+        <v>69.827520173329702</v>
       </c>
       <c r="AL30" s="0">
         <v>0</v>
@@ -3700,112 +3700,112 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>25.0670180241537</v>
+        <v>25.067018024158202</v>
       </c>
       <c r="C31" s="0">
-        <v>54.134036048307401</v>
+        <v>54.134036048316297</v>
       </c>
       <c r="D31" s="0">
-        <v>57.8764380701231</v>
+        <v>57.876438070132103</v>
       </c>
       <c r="E31" s="0">
-        <v>30.6184193347936</v>
+        <v>30.618420934829</v>
       </c>
       <c r="F31" s="0">
-        <v>67.236838669587101</v>
+        <v>67.236841869658093</v>
       </c>
       <c r="G31" s="0">
-        <v>72.850441702310803</v>
+        <v>72.850444902381795</v>
       </c>
       <c r="H31" s="0">
-        <v>25.067018024202898</v>
+        <v>25.0670180241701</v>
       </c>
       <c r="I31" s="0">
-        <v>56.134036048405697</v>
+        <v>56.1340360483401</v>
       </c>
       <c r="J31" s="0">
-        <v>61.7476390811294</v>
+        <v>61.747639081063802</v>
       </c>
       <c r="K31" s="0">
-        <v>30.618420934761598</v>
+        <v>30.6184193347563</v>
       </c>
       <c r="L31" s="0">
-        <v>69.236841869523303</v>
+        <v>69.236838669512494</v>
       </c>
       <c r="M31" s="0">
-        <v>76.721645913154802</v>
+        <v>76.721642713144107</v>
       </c>
       <c r="N31" s="0">
-        <v>22.486494775672099</v>
+        <v>25.067019630549101</v>
       </c>
       <c r="O31" s="0">
-        <v>48.972989551344298</v>
+        <v>54.134039261098202</v>
       </c>
       <c r="P31" s="0">
-        <v>52.715391573159998</v>
+        <v>57.876441282914001</v>
       </c>
       <c r="Q31" s="0">
-        <v>27.0216979582083</v>
+        <v>30.618419336712101</v>
       </c>
       <c r="R31" s="0">
-        <v>60.0433959164166</v>
+        <v>67.236838673424202</v>
       </c>
       <c r="S31" s="0">
-        <v>65.656998949140302</v>
+        <v>72.850441706147905</v>
       </c>
       <c r="T31" s="0">
-        <v>23.375621688338001</v>
+        <v>25.067019624152501</v>
       </c>
       <c r="U31" s="0">
-        <v>52.751243376676001</v>
+        <v>56.134039248305101</v>
       </c>
       <c r="V31" s="0">
-        <v>58.364846409399597</v>
+        <v>61.747642281028703</v>
       </c>
       <c r="W31" s="0">
-        <v>27.021697958096201</v>
+        <v>30.6184193347598</v>
       </c>
       <c r="X31" s="0">
-        <v>62.043395916192402</v>
+        <v>69.236838669519599</v>
       </c>
       <c r="Y31" s="0">
-        <v>69.528199959823993</v>
+        <v>76.721642713151198</v>
       </c>
       <c r="Z31" s="0">
-        <v>24.6475216473175</v>
+        <v>25.067018024189</v>
       </c>
       <c r="AA31" s="0">
-        <v>53.2950432946351</v>
+        <v>54.134036048378</v>
       </c>
       <c r="AB31" s="0">
-        <v>57.037445316450899</v>
+        <v>57.876438070193799</v>
       </c>
       <c r="AC31" s="0">
-        <v>28.634417275167898</v>
+        <v>30.618419134758302</v>
       </c>
       <c r="AD31" s="0">
-        <v>63.268834550335697</v>
+        <v>67.236838269516596</v>
       </c>
       <c r="AE31" s="0">
-        <v>68.882437583059399</v>
+        <v>72.850441302240299</v>
       </c>
       <c r="AF31" s="0">
-        <v>24.961684628070198</v>
+        <v>25.067018024153501</v>
       </c>
       <c r="AG31" s="0">
-        <v>55.923369256140298</v>
+        <v>56.134036048307003</v>
       </c>
       <c r="AH31" s="0">
-        <v>61.536972288864</v>
+        <v>61.747639081030698</v>
       </c>
       <c r="AI31" s="0">
-        <v>28.634417327888901</v>
+        <v>30.618420934763002</v>
       </c>
       <c r="AJ31" s="0">
-        <v>65.268834655777695</v>
+        <v>69.236841869525904</v>
       </c>
       <c r="AK31" s="0">
-        <v>72.753638699409294</v>
+        <v>76.721645913157502</v>
       </c>
       <c r="AL31" s="0">
         <v>0</v>
@@ -3816,22 +3816,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>20.0632734196043</v>
+        <v>20.063273419604201</v>
       </c>
       <c r="C32" s="0">
-        <v>44.126546839208501</v>
+        <v>44.126546839208302</v>
       </c>
       <c r="D32" s="0">
-        <v>47.8689488610243</v>
+        <v>47.868948861024101</v>
       </c>
       <c r="E32" s="0">
-        <v>28.7636909143006</v>
+        <v>28.763690914300501</v>
       </c>
       <c r="F32" s="0">
-        <v>63.527381828601101</v>
+        <v>63.527381828601001</v>
       </c>
       <c r="G32" s="0">
-        <v>69.140984861324796</v>
+        <v>69.140984861324696</v>
       </c>
       <c r="H32" s="0">
         <v>25.416774730708099</v>
@@ -3846,82 +3846,82 @@
         <v>28.763690914300501</v>
       </c>
       <c r="L32" s="0">
-        <v>65.527381828600994</v>
+        <v>65.527381828601094</v>
       </c>
       <c r="M32" s="0">
-        <v>73.012185872232493</v>
+        <v>73.012185872232607</v>
       </c>
       <c r="N32" s="0">
-        <v>22.234101178053901</v>
+        <v>22.234101176039999</v>
       </c>
       <c r="O32" s="0">
-        <v>48.468202356107803</v>
+        <v>48.468202352079999</v>
       </c>
       <c r="P32" s="0">
-        <v>52.210604377923602</v>
+        <v>52.210604373895798</v>
       </c>
       <c r="Q32" s="0">
-        <v>29.2141803656626</v>
+        <v>29.21418036327</v>
       </c>
       <c r="R32" s="0">
-        <v>64.428360731325199</v>
+        <v>64.428360726540006</v>
       </c>
       <c r="S32" s="0">
-        <v>70.041963764048802</v>
+        <v>70.041963759263695</v>
       </c>
       <c r="T32" s="0">
-        <v>25.878798312607501</v>
+        <v>25.878798309571899</v>
       </c>
       <c r="U32" s="0">
-        <v>57.757596625215001</v>
+        <v>57.757596619143797</v>
       </c>
       <c r="V32" s="0">
-        <v>63.371199657938597</v>
+        <v>63.371199651867499</v>
       </c>
       <c r="W32" s="0">
-        <v>29.214180367506501</v>
+        <v>29.21418036327</v>
       </c>
       <c r="X32" s="0">
-        <v>66.428360735013001</v>
+        <v>66.428360726540006</v>
       </c>
       <c r="Y32" s="0">
-        <v>73.9131647786446</v>
+        <v>73.913164770171605</v>
       </c>
       <c r="Z32" s="0">
-        <v>21.0724481414838</v>
+        <v>21.0724481384458</v>
       </c>
       <c r="AA32" s="0">
-        <v>46.144896282967601</v>
+        <v>46.1448962768917</v>
       </c>
       <c r="AB32" s="0">
-        <v>49.8872983047834</v>
+        <v>49.887298298707499</v>
       </c>
       <c r="AC32" s="0">
-        <v>28.255057461599598</v>
+        <v>28.255057460981199</v>
       </c>
       <c r="AD32" s="0">
-        <v>62.510114923199197</v>
+        <v>62.510114921962298</v>
       </c>
       <c r="AE32" s="0">
-        <v>68.123717955922899</v>
+        <v>68.123717954686001</v>
       </c>
       <c r="AF32" s="0">
-        <v>26.151631279039499</v>
+        <v>26.151631277196699</v>
       </c>
       <c r="AG32" s="0">
-        <v>58.303262558078998</v>
+        <v>58.303262554393399</v>
       </c>
       <c r="AH32" s="0">
-        <v>63.916865590802601</v>
+        <v>63.916865587117101</v>
       </c>
       <c r="AI32" s="0">
-        <v>28.2550574611926</v>
+        <v>28.255057460980801</v>
       </c>
       <c r="AJ32" s="0">
-        <v>64.5101149223851</v>
+        <v>64.510114921961701</v>
       </c>
       <c r="AK32" s="0">
-        <v>71.994918966016698</v>
+        <v>71.9949189655933</v>
       </c>
       <c r="AL32" s="0">
         <v>0</v>
@@ -3932,112 +3932,112 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>17.366872368750599</v>
+        <v>17.366872688769298</v>
       </c>
       <c r="C33" s="0">
-        <v>38.733744737501198</v>
+        <v>38.733745377538497</v>
       </c>
       <c r="D33" s="0">
-        <v>42.476146759316997</v>
+        <v>42.476147399354304</v>
       </c>
       <c r="E33" s="0">
-        <v>27.171358064847698</v>
+        <v>27.171356084850199</v>
       </c>
       <c r="F33" s="0">
-        <v>60.342716129695397</v>
+        <v>60.342712169700299</v>
       </c>
       <c r="G33" s="0">
-        <v>65.956319162419007</v>
+        <v>65.956315202423994</v>
       </c>
       <c r="H33" s="0">
-        <v>17.366872688749801</v>
+        <v>17.366872688773899</v>
       </c>
       <c r="I33" s="0">
-        <v>40.733745377499503</v>
+        <v>40.733745377547699</v>
       </c>
       <c r="J33" s="0">
-        <v>46.347348410223198</v>
+        <v>46.347348410271401</v>
       </c>
       <c r="K33" s="0">
-        <v>27.171358064848199</v>
+        <v>27.171356084850299</v>
       </c>
       <c r="L33" s="0">
-        <v>62.342716129696299</v>
+        <v>62.342712169700697</v>
       </c>
       <c r="M33" s="0">
-        <v>69.827520173327898</v>
+        <v>69.827516213332203</v>
       </c>
       <c r="N33" s="0">
-        <v>10.9913799325405</v>
+        <v>17.3668726887582</v>
       </c>
       <c r="O33" s="0">
-        <v>25.982759865081</v>
+        <v>38.733745377516399</v>
       </c>
       <c r="P33" s="0">
-        <v>29.7251618868968</v>
+        <v>42.476147399332099</v>
       </c>
       <c r="Q33" s="0">
-        <v>21.2155759639782</v>
+        <v>27.171358064848999</v>
       </c>
       <c r="R33" s="0">
-        <v>48.431151927956499</v>
+        <v>60.342716129697898</v>
       </c>
       <c r="S33" s="0">
-        <v>54.044754960680201</v>
+        <v>65.956319162421593</v>
       </c>
       <c r="T33" s="0">
-        <v>13.7994605843654</v>
+        <v>17.366874288749202</v>
       </c>
       <c r="U33" s="0">
-        <v>33.598921168730698</v>
+        <v>40.733748577498297</v>
       </c>
       <c r="V33" s="0">
-        <v>39.2125242014544</v>
+        <v>46.347351610221999</v>
       </c>
       <c r="W33" s="0">
-        <v>21.2155759639124</v>
+        <v>27.1713580648495</v>
       </c>
       <c r="X33" s="0">
-        <v>50.431151927824899</v>
+        <v>62.3427161296989</v>
       </c>
       <c r="Y33" s="0">
-        <v>57.915955971456398</v>
+        <v>69.827520173330498</v>
       </c>
       <c r="Z33" s="0">
-        <v>13.423977469866699</v>
+        <v>17.366872688749901</v>
       </c>
       <c r="AA33" s="0">
-        <v>30.847954939733299</v>
+        <v>38.733745377499901</v>
       </c>
       <c r="AB33" s="0">
-        <v>34.590356961549098</v>
+        <v>42.4761473993156</v>
       </c>
       <c r="AC33" s="0">
-        <v>23.379640285975398</v>
+        <v>27.171356464851101</v>
       </c>
       <c r="AD33" s="0">
-        <v>52.759280571950697</v>
+        <v>60.342712929702202</v>
       </c>
       <c r="AE33" s="0">
-        <v>58.372883604674399</v>
+        <v>65.956315962425904</v>
       </c>
       <c r="AF33" s="0">
-        <v>15.551831243756601</v>
+        <v>17.366874298577599</v>
       </c>
       <c r="AG33" s="0">
-        <v>37.103662487513198</v>
+        <v>40.733748597155198</v>
       </c>
       <c r="AH33" s="0">
-        <v>42.717265520236801</v>
+        <v>46.347351629878801</v>
       </c>
       <c r="AI33" s="0">
-        <v>23.379640217782899</v>
+        <v>27.171358088690202</v>
       </c>
       <c r="AJ33" s="0">
-        <v>54.759280435565699</v>
+        <v>62.342716177380503</v>
       </c>
       <c r="AK33" s="0">
-        <v>62.244084479197298</v>
+        <v>69.827520221011994</v>
       </c>
       <c r="AL33" s="0">
         <v>0</v>
@@ -4057,103 +4057,103 @@
         <v>69.1135431502762</v>
       </c>
       <c r="E34" s="0">
-        <v>31.367181554200901</v>
+        <v>31.367183076174499</v>
       </c>
       <c r="F34" s="0">
-        <v>68.734363108401894</v>
+        <v>68.734366152349097</v>
       </c>
       <c r="G34" s="0">
-        <v>74.347966141125497</v>
+        <v>74.347969185072699</v>
       </c>
       <c r="H34" s="0">
-        <v>31.183979311297101</v>
+        <v>31.1839793112979</v>
       </c>
       <c r="I34" s="0">
-        <v>68.367958622594202</v>
+        <v>68.367958622595793</v>
       </c>
       <c r="J34" s="0">
-        <v>73.981561655317904</v>
+        <v>73.981561655319396</v>
       </c>
       <c r="K34" s="0">
-        <v>31.367181554256099</v>
+        <v>31.367183542766401</v>
       </c>
       <c r="L34" s="0">
-        <v>70.734363108512198</v>
+        <v>70.734367085532895</v>
       </c>
       <c r="M34" s="0">
-        <v>78.219167152143697</v>
+        <v>78.219171129164394</v>
       </c>
       <c r="N34" s="0">
-        <v>31.182112419486501</v>
+        <v>31.1839773912989</v>
       </c>
       <c r="O34" s="0">
-        <v>66.364224838972902</v>
+        <v>66.367954782597806</v>
       </c>
       <c r="P34" s="0">
-        <v>70.106626860788694</v>
+        <v>70.110356804413598</v>
       </c>
       <c r="Q34" s="0">
-        <v>30.1829001735661</v>
+        <v>31.3671815541855</v>
       </c>
       <c r="R34" s="0">
-        <v>66.365800347132307</v>
+        <v>68.734363108371099</v>
       </c>
       <c r="S34" s="0">
-        <v>71.979403379855896</v>
+        <v>74.347966141094702</v>
       </c>
       <c r="T34" s="0">
-        <v>29.764661835745098</v>
+        <v>31.183977331303101</v>
       </c>
       <c r="U34" s="0">
-        <v>65.529323671490303</v>
+        <v>68.367954662606195</v>
       </c>
       <c r="V34" s="0">
-        <v>71.142926704213906</v>
+        <v>73.981557695329798</v>
       </c>
       <c r="W34" s="0">
-        <v>30.182900173558401</v>
+        <v>31.367181554170099</v>
       </c>
       <c r="X34" s="0">
-        <v>68.365800347116803</v>
+        <v>70.734363108340105</v>
       </c>
       <c r="Y34" s="0">
-        <v>75.850604390748401</v>
+        <v>78.219167151971703</v>
       </c>
       <c r="Z34" s="0">
-        <v>31.0963423696044</v>
+        <v>31.096342364251701</v>
       </c>
       <c r="AA34" s="0">
-        <v>66.1926847392089</v>
+        <v>66.192684728503394</v>
       </c>
       <c r="AB34" s="0">
-        <v>69.935086761024607</v>
+        <v>69.935086750319101</v>
       </c>
       <c r="AC34" s="0">
-        <v>30.6165412617868</v>
+        <v>31.367181874121801</v>
       </c>
       <c r="AD34" s="0">
-        <v>67.2330825235737</v>
+        <v>68.734363748243695</v>
       </c>
       <c r="AE34" s="0">
-        <v>72.846685556297302</v>
+        <v>74.347966780967297</v>
       </c>
       <c r="AF34" s="0">
-        <v>30.160668020470801</v>
+        <v>31.1839793112979</v>
       </c>
       <c r="AG34" s="0">
-        <v>66.321336040941603</v>
+        <v>68.367958622595694</v>
       </c>
       <c r="AH34" s="0">
-        <v>71.934939073665305</v>
+        <v>73.981561655319396</v>
       </c>
       <c r="AI34" s="0">
-        <v>30.6165412570755</v>
+        <v>31.367181874121702</v>
       </c>
       <c r="AJ34" s="0">
-        <v>69.233082514151107</v>
+        <v>70.734363748243396</v>
       </c>
       <c r="AK34" s="0">
-        <v>76.717886557782606</v>
+        <v>78.219167791874995</v>
       </c>
       <c r="AL34" s="0">
         <v>1</v>
@@ -4164,112 +4164,112 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>14.893410335029399</v>
+        <v>14.893370735333299</v>
       </c>
       <c r="C35" s="0">
-        <v>33.786820670058802</v>
+        <v>33.786741470666598</v>
       </c>
       <c r="D35" s="0">
-        <v>37.529222691874502</v>
+        <v>37.529143492482397</v>
       </c>
       <c r="E35" s="0">
-        <v>25.318970077811901</v>
+        <v>25.318968879528899</v>
       </c>
       <c r="F35" s="0">
-        <v>56.637940155623802</v>
+        <v>56.637937759057898</v>
       </c>
       <c r="G35" s="0">
-        <v>62.251543188347497</v>
+        <v>62.251540791781601</v>
       </c>
       <c r="H35" s="0">
-        <v>14.8933707352939</v>
+        <v>14.8933707353739</v>
       </c>
       <c r="I35" s="0">
-        <v>35.786741470587899</v>
+        <v>35.7867414707477</v>
       </c>
       <c r="J35" s="0">
-        <v>41.400344503311501</v>
+        <v>41.400344503471402</v>
       </c>
       <c r="K35" s="0">
-        <v>25.318968879392099</v>
+        <v>25.318968877813699</v>
       </c>
       <c r="L35" s="0">
-        <v>58.637937758784297</v>
+        <v>58.637937755627398</v>
       </c>
       <c r="M35" s="0">
-        <v>66.122741802415803</v>
+        <v>66.122741799258904</v>
       </c>
       <c r="N35" s="0">
-        <v>11.188946189548201</v>
+        <v>14.8933707352941</v>
       </c>
       <c r="O35" s="0">
-        <v>26.377892379096401</v>
+        <v>33.786741470588197</v>
       </c>
       <c r="P35" s="0">
-        <v>30.120294400912201</v>
+        <v>37.529143492404003</v>
       </c>
       <c r="Q35" s="0">
-        <v>22.9158193622727</v>
+        <v>25.318968877844299</v>
       </c>
       <c r="R35" s="0">
-        <v>51.8316387245454</v>
+        <v>56.637937755688696</v>
       </c>
       <c r="S35" s="0">
-        <v>57.445241757269102</v>
+        <v>62.251540788412299</v>
       </c>
       <c r="T35" s="0">
-        <v>13.1871246218175</v>
+        <v>14.893370735307601</v>
       </c>
       <c r="U35" s="0">
-        <v>32.374249243634999</v>
+        <v>35.786741470615198</v>
       </c>
       <c r="V35" s="0">
-        <v>37.987852276358602</v>
+        <v>41.4003445033389</v>
       </c>
       <c r="W35" s="0">
-        <v>22.915819362354</v>
+        <v>25.318968877844199</v>
       </c>
       <c r="X35" s="0">
-        <v>53.831638724708</v>
+        <v>58.637937755688498</v>
       </c>
       <c r="Y35" s="0">
-        <v>61.316442768339499</v>
+        <v>66.122741799319996</v>
       </c>
       <c r="Z35" s="0">
-        <v>13.256743074254</v>
+        <v>14.893370735322501</v>
       </c>
       <c r="AA35" s="0">
-        <v>30.513486148507901</v>
+        <v>33.786741470644898</v>
       </c>
       <c r="AB35" s="0">
-        <v>34.255888170323701</v>
+        <v>37.529143492460697</v>
       </c>
       <c r="AC35" s="0">
-        <v>24.642576742495301</v>
+        <v>25.318968877816101</v>
       </c>
       <c r="AD35" s="0">
-        <v>55.285153484990602</v>
+        <v>56.637937755632102</v>
       </c>
       <c r="AE35" s="0">
-        <v>60.898756517714297</v>
+        <v>62.251540788355797</v>
       </c>
       <c r="AF35" s="0">
-        <v>14.5606898455605</v>
+        <v>14.8933723352919</v>
       </c>
       <c r="AG35" s="0">
-        <v>35.121379691121099</v>
+        <v>35.786744670583701</v>
       </c>
       <c r="AH35" s="0">
-        <v>40.734982723844702</v>
+        <v>41.400347703307403</v>
       </c>
       <c r="AI35" s="0">
-        <v>24.642576742888199</v>
+        <v>25.318968877813699</v>
       </c>
       <c r="AJ35" s="0">
-        <v>57.285153485776398</v>
+        <v>58.637937755627497</v>
       </c>
       <c r="AK35" s="0">
-        <v>64.769957529408003</v>
+        <v>66.122741799259003</v>
       </c>
       <c r="AL35" s="0">
         <v>1</v>
@@ -4280,112 +4280,112 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>10.3825266547446</v>
+        <v>10.382526656553599</v>
       </c>
       <c r="C36" s="0">
-        <v>24.7650533094893</v>
+        <v>24.765053313107099</v>
       </c>
       <c r="D36" s="0">
-        <v>28.507455331305</v>
+        <v>28.507455334922899</v>
       </c>
       <c r="E36" s="0">
-        <v>21.826795664959601</v>
+        <v>21.826795720501298</v>
       </c>
       <c r="F36" s="0">
-        <v>49.653591329919102</v>
+        <v>49.653591441002497</v>
       </c>
       <c r="G36" s="0">
-        <v>55.267194362642798</v>
+        <v>55.2671944737262</v>
       </c>
       <c r="H36" s="0">
-        <v>10.736440804468</v>
+        <v>10.736440771835699</v>
       </c>
       <c r="I36" s="0">
-        <v>27.4728816089359</v>
+        <v>27.472881543671399</v>
       </c>
       <c r="J36" s="0">
-        <v>33.086484641659602</v>
+        <v>33.086484576395002</v>
       </c>
       <c r="K36" s="0">
-        <v>21.827070280449099</v>
+        <v>21.826795650570102</v>
       </c>
       <c r="L36" s="0">
-        <v>51.654140560898298</v>
+        <v>51.653591301140203</v>
       </c>
       <c r="M36" s="0">
-        <v>59.138944604529797</v>
+        <v>59.138395344771702</v>
       </c>
       <c r="N36" s="0">
-        <v>11.023541862128299</v>
+        <v>11.023541870949099</v>
       </c>
       <c r="O36" s="0">
-        <v>26.047083724256701</v>
+        <v>26.047083741898099</v>
       </c>
       <c r="P36" s="0">
-        <v>29.789485746072401</v>
+        <v>29.789485763713898</v>
       </c>
       <c r="Q36" s="0">
-        <v>22.147303264502899</v>
+        <v>22.147303264501701</v>
       </c>
       <c r="R36" s="0">
-        <v>50.294606529005797</v>
+        <v>50.294606529003502</v>
       </c>
       <c r="S36" s="0">
-        <v>55.9082095617295</v>
+        <v>55.908209561727098</v>
       </c>
       <c r="T36" s="0">
-        <v>11.056948375543801</v>
+        <v>11.056948400405799</v>
       </c>
       <c r="U36" s="0">
-        <v>28.113896751087498</v>
+        <v>28.113896800811599</v>
       </c>
       <c r="V36" s="0">
-        <v>33.727499783811197</v>
+        <v>33.727499833535298</v>
       </c>
       <c r="W36" s="0">
-        <v>22.147303264504</v>
+        <v>22.1473032668687</v>
       </c>
       <c r="X36" s="0">
-        <v>52.294606529007901</v>
+        <v>52.2946065337375</v>
       </c>
       <c r="Y36" s="0">
-        <v>59.779410572639499</v>
+        <v>59.779410577369099</v>
       </c>
       <c r="Z36" s="0">
-        <v>-0</v>
+        <v>11.024356489893099</v>
       </c>
       <c r="AA36" s="0">
-        <v>4</v>
+        <v>26.048712979786199</v>
       </c>
       <c r="AB36" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.791115001602002</v>
       </c>
       <c r="AC36" s="0">
-        <v>16.6355323334387</v>
+        <v>22.147673242869899</v>
       </c>
       <c r="AD36" s="0">
-        <v>39.2710646668774</v>
+        <v>50.295346485739699</v>
       </c>
       <c r="AE36" s="0">
-        <v>44.884667699601003</v>
+        <v>55.908949518463402</v>
       </c>
       <c r="AF36" s="0">
-        <v>-0</v>
+        <v>11.0572951824226</v>
       </c>
       <c r="AG36" s="0">
-        <v>6</v>
+        <v>28.114590364845199</v>
       </c>
       <c r="AH36" s="0">
-        <v>11.613603032723701</v>
+        <v>33.728193397568901</v>
       </c>
       <c r="AI36" s="0">
-        <v>16.6355323334387</v>
+        <v>22.148718055233399</v>
       </c>
       <c r="AJ36" s="0">
-        <v>41.2710646668774</v>
+        <v>52.297436110466698</v>
       </c>
       <c r="AK36" s="0">
-        <v>48.755868710508899</v>
+        <v>59.782240154098297</v>
       </c>
       <c r="AL36" s="0">
         <v>1</v>
@@ -4396,112 +4396,112 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>11.090362992947901</v>
+        <v>11.090362987776</v>
       </c>
       <c r="C37" s="0">
-        <v>26.180725985895801</v>
+        <v>26.180725975552001</v>
       </c>
       <c r="D37" s="0">
-        <v>29.9231280077116</v>
+        <v>29.9231279973677</v>
       </c>
       <c r="E37" s="0">
-        <v>22.180717915924799</v>
+        <v>22.180715624293001</v>
       </c>
       <c r="F37" s="0">
-        <v>50.361435831849597</v>
+        <v>50.361431248586001</v>
       </c>
       <c r="G37" s="0">
-        <v>55.9750388645733</v>
+        <v>55.975034281309597</v>
       </c>
       <c r="H37" s="0">
-        <v>11.0903565186681</v>
+        <v>11.0903552899705</v>
       </c>
       <c r="I37" s="0">
-        <v>28.1807130373363</v>
+        <v>28.1807105799409</v>
       </c>
       <c r="J37" s="0">
-        <v>33.794316070059899</v>
+        <v>33.794313612664602</v>
       </c>
       <c r="K37" s="0">
-        <v>22.180711383534899</v>
+        <v>22.1807505238598</v>
       </c>
       <c r="L37" s="0">
-        <v>52.361422767069797</v>
+        <v>52.3615010477195</v>
       </c>
       <c r="M37" s="0">
-        <v>59.846226810701303</v>
+        <v>59.846305091351098</v>
       </c>
       <c r="N37" s="0">
-        <v>5.0264895789472197</v>
+        <v>11.0903565093151</v>
       </c>
       <c r="O37" s="0">
-        <v>14.0529791578944</v>
+        <v>26.1807130186302</v>
       </c>
       <c r="P37" s="0">
-        <v>17.795381179710201</v>
+        <v>29.923115040446</v>
       </c>
       <c r="Q37" s="0">
-        <v>20.314917162299299</v>
+        <v>22.180717555267702</v>
       </c>
       <c r="R37" s="0">
-        <v>46.629834324598498</v>
+        <v>50.361435110535297</v>
       </c>
       <c r="S37" s="0">
-        <v>52.2434373573222</v>
+        <v>55.975038143258999</v>
       </c>
       <c r="T37" s="0">
-        <v>9.2245622733401795</v>
+        <v>11.0903629799465</v>
       </c>
       <c r="U37" s="0">
-        <v>24.449124546680402</v>
+        <v>28.180725959893</v>
       </c>
       <c r="V37" s="0">
-        <v>30.062727579404001</v>
+        <v>33.794328992616599</v>
       </c>
       <c r="W37" s="0">
-        <v>20.314917162299501</v>
+        <v>22.1807105173935</v>
       </c>
       <c r="X37" s="0">
-        <v>48.629834324599003</v>
+        <v>52.3614210347869</v>
       </c>
       <c r="Y37" s="0">
-        <v>56.114638368230501</v>
+        <v>59.846225078418499</v>
       </c>
       <c r="Z37" s="0">
-        <v>-0</v>
+        <v>11.090362996469601</v>
       </c>
       <c r="AA37" s="0">
-        <v>4</v>
+        <v>26.180725992939099</v>
       </c>
       <c r="AB37" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923128014754901</v>
       </c>
       <c r="AC37" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180749760408698</v>
       </c>
       <c r="AD37" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361499520817297</v>
       </c>
       <c r="AE37" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975102553540999</v>
       </c>
       <c r="AF37" s="0">
-        <v>-0</v>
+        <v>11.0903565090178</v>
       </c>
       <c r="AG37" s="0">
-        <v>6</v>
+        <v>28.1807130180356</v>
       </c>
       <c r="AH37" s="0">
-        <v>11.613603032723701</v>
+        <v>33.794316050759299</v>
       </c>
       <c r="AI37" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180712383750802</v>
       </c>
       <c r="AJ37" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361424767501497</v>
       </c>
       <c r="AK37" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846228811133102</v>
       </c>
       <c r="AL37" s="0">
         <v>1</v>
@@ -4512,112 +4512,112 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C38" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D38" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E38" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F38" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G38" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H38" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I38" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J38" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K38" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L38" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M38" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N38" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O38" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P38" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q38" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R38" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S38" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T38" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U38" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V38" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W38" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X38" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y38" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z38" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA38" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB38" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC38" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD38" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE38" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF38" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG38" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH38" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI38" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ38" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK38" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL38" s="0">
         <v>1</v>
@@ -4628,112 +4628,112 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C39" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D39" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E39" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F39" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G39" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H39" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I39" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J39" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K39" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L39" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M39" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N39" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O39" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P39" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q39" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R39" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S39" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T39" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U39" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V39" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W39" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X39" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y39" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z39" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA39" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB39" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC39" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD39" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE39" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF39" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG39" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH39" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI39" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ39" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK39" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL39" s="0">
         <v>1</v>
@@ -4744,112 +4744,112 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>22.5615590413103</v>
+        <v>22.561559041325701</v>
       </c>
       <c r="C40" s="0">
-        <v>49.123118082620501</v>
+        <v>49.123118082651402</v>
       </c>
       <c r="D40" s="0">
-        <v>52.8655201044363</v>
+        <v>52.865520104467201</v>
       </c>
       <c r="E40" s="0">
-        <v>28.577265301685099</v>
+        <v>28.577259301697101</v>
       </c>
       <c r="F40" s="0">
-        <v>63.154530603370198</v>
+        <v>63.154518603394301</v>
       </c>
       <c r="G40" s="0">
-        <v>68.768133636093907</v>
+        <v>68.768121636117897</v>
       </c>
       <c r="H40" s="0">
-        <v>22.561559041355999</v>
+        <v>22.5615590413592</v>
       </c>
       <c r="I40" s="0">
-        <v>51.123118082711997</v>
+        <v>51.123118082718399</v>
       </c>
       <c r="J40" s="0">
-        <v>56.736721115435699</v>
+        <v>56.736721115442002</v>
       </c>
       <c r="K40" s="0">
-        <v>28.577257701699299</v>
+        <v>28.5772573817564</v>
       </c>
       <c r="L40" s="0">
-        <v>65.154515403398605</v>
+        <v>65.154514763512793</v>
       </c>
       <c r="M40" s="0">
-        <v>72.639319447030203</v>
+        <v>72.639318807144306</v>
       </c>
       <c r="N40" s="0">
-        <v>14.0664915122358</v>
+        <v>22.5615686413059</v>
       </c>
       <c r="O40" s="0">
-        <v>32.1329830244715</v>
+        <v>49.123137282611701</v>
       </c>
       <c r="P40" s="0">
-        <v>35.875385046287299</v>
+        <v>52.8655393044275</v>
       </c>
       <c r="Q40" s="0">
-        <v>25.475619219659698</v>
+        <v>28.577257701723699</v>
       </c>
       <c r="R40" s="0">
-        <v>56.951238439319297</v>
+        <v>63.154515403447299</v>
       </c>
       <c r="S40" s="0">
-        <v>62.564841472043</v>
+        <v>68.768118436170994</v>
       </c>
       <c r="T40" s="0">
-        <v>20.5344137821583</v>
+        <v>22.561560662153202</v>
       </c>
       <c r="U40" s="0">
-        <v>47.0688275643165</v>
+        <v>51.123121324306297</v>
       </c>
       <c r="V40" s="0">
-        <v>52.682430597040202</v>
+        <v>56.736724357029999</v>
       </c>
       <c r="W40" s="0">
-        <v>25.475619219654501</v>
+        <v>28.577257701722299</v>
       </c>
       <c r="X40" s="0">
-        <v>58.951238439309101</v>
+        <v>65.154515403444606</v>
       </c>
       <c r="Y40" s="0">
-        <v>66.436042482940607</v>
+        <v>72.639319447076204</v>
       </c>
       <c r="Z40" s="0">
-        <v>18.618515386841501</v>
+        <v>22.561559641297499</v>
       </c>
       <c r="AA40" s="0">
-        <v>41.237030773682903</v>
+        <v>49.123119282595098</v>
       </c>
       <c r="AB40" s="0">
-        <v>44.979432795498703</v>
+        <v>52.865521304410898</v>
       </c>
       <c r="AC40" s="0">
-        <v>27.539443082781698</v>
+        <v>28.577257317699502</v>
       </c>
       <c r="AD40" s="0">
-        <v>61.078886165563297</v>
+        <v>63.154514635399003</v>
       </c>
       <c r="AE40" s="0">
-        <v>66.692489198287007</v>
+        <v>68.768117668122699</v>
       </c>
       <c r="AF40" s="0">
-        <v>22.183206844380202</v>
+        <v>22.561560682369901</v>
       </c>
       <c r="AG40" s="0">
-        <v>50.366413688760503</v>
+        <v>51.123121364739802</v>
       </c>
       <c r="AH40" s="0">
-        <v>55.980016721484098</v>
+        <v>56.736724397463497</v>
       </c>
       <c r="AI40" s="0">
-        <v>27.539443084248798</v>
+        <v>28.577257321698799</v>
       </c>
       <c r="AJ40" s="0">
-        <v>63.078886168497498</v>
+        <v>65.154514643397604</v>
       </c>
       <c r="AK40" s="0">
-        <v>70.563690212129103</v>
+        <v>72.639318687029203</v>
       </c>
       <c r="AL40" s="0">
         <v>1</v>
@@ -4860,112 +4860,112 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>17.366872368749799</v>
+        <v>17.366872304749801</v>
       </c>
       <c r="C41" s="0">
-        <v>38.733744737499499</v>
+        <v>38.733744609499702</v>
       </c>
       <c r="D41" s="0">
-        <v>42.476146759315299</v>
+        <v>42.476146631315501</v>
       </c>
       <c r="E41" s="0">
-        <v>25.315267152893998</v>
+        <v>25.315267152997301</v>
       </c>
       <c r="F41" s="0">
-        <v>56.630534305788103</v>
+        <v>56.630534305994601</v>
       </c>
       <c r="G41" s="0">
-        <v>62.244137338511798</v>
+        <v>62.244137338718303</v>
       </c>
       <c r="H41" s="0">
-        <v>17.363522432478099</v>
+        <v>17.363522432467999</v>
       </c>
       <c r="I41" s="0">
-        <v>40.727044864956099</v>
+        <v>40.727044864935898</v>
       </c>
       <c r="J41" s="0">
-        <v>46.340647897679801</v>
+        <v>46.340647897659601</v>
       </c>
       <c r="K41" s="0">
-        <v>25.3152671528944</v>
+        <v>25.315267152899899</v>
       </c>
       <c r="L41" s="0">
-        <v>58.630534305788899</v>
+        <v>58.630534305799699</v>
       </c>
       <c r="M41" s="0">
-        <v>66.115338349420497</v>
+        <v>66.115338349431298</v>
       </c>
       <c r="N41" s="0">
-        <v>16.8987691265033</v>
+        <v>17.36687248874</v>
       </c>
       <c r="O41" s="0">
-        <v>37.7975382530066</v>
+        <v>38.7337449774801</v>
       </c>
       <c r="P41" s="0">
-        <v>41.539940274822399</v>
+        <v>42.476146999295899</v>
       </c>
       <c r="Q41" s="0">
-        <v>25.317004155429998</v>
+        <v>25.318968877826499</v>
       </c>
       <c r="R41" s="0">
-        <v>56.634008310859997</v>
+        <v>56.637937755652999</v>
       </c>
       <c r="S41" s="0">
-        <v>62.2476113435836</v>
+        <v>62.251540788376701</v>
       </c>
       <c r="T41" s="0">
-        <v>17.365153733721801</v>
+        <v>17.366872688818599</v>
       </c>
       <c r="U41" s="0">
-        <v>40.730307467443502</v>
+        <v>40.733745377637199</v>
       </c>
       <c r="V41" s="0">
-        <v>46.343910500167198</v>
+        <v>46.347348410360901</v>
       </c>
       <c r="W41" s="0">
-        <v>25.317004154847201</v>
+        <v>25.3189688777925</v>
       </c>
       <c r="X41" s="0">
-        <v>58.634008309694401</v>
+        <v>58.637937755585099</v>
       </c>
       <c r="Y41" s="0">
-        <v>66.118812353325893</v>
+        <v>66.122741799216698</v>
       </c>
       <c r="Z41" s="0">
-        <v>17.127889630755</v>
+        <v>17.366872688765898</v>
       </c>
       <c r="AA41" s="0">
-        <v>38.25577926151</v>
+        <v>38.733745377531903</v>
       </c>
       <c r="AB41" s="0">
-        <v>41.998181283325799</v>
+        <v>42.476147399347603</v>
       </c>
       <c r="AC41" s="0">
-        <v>25.317578250632799</v>
+        <v>25.317578250108198</v>
       </c>
       <c r="AD41" s="0">
-        <v>56.635156501265598</v>
+        <v>56.635156500216397</v>
       </c>
       <c r="AE41" s="0">
-        <v>62.248759533989301</v>
+        <v>62.248759532940099</v>
       </c>
       <c r="AF41" s="0">
-        <v>17.365968409344099</v>
+        <v>17.365968409130598</v>
       </c>
       <c r="AG41" s="0">
-        <v>40.731936818688098</v>
+        <v>40.731936818261303</v>
       </c>
       <c r="AH41" s="0">
-        <v>46.3455398514118</v>
+        <v>46.345539850984899</v>
       </c>
       <c r="AI41" s="0">
-        <v>25.317578250354298</v>
+        <v>25.317578250107601</v>
       </c>
       <c r="AJ41" s="0">
-        <v>58.635156500708703</v>
+        <v>58.635156500215302</v>
       </c>
       <c r="AK41" s="0">
-        <v>66.119960544340302</v>
+        <v>66.119960543846801</v>
       </c>
       <c r="AL41" s="0">
         <v>1</v>
@@ -4976,112 +4976,112 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>11.0903629519454</v>
+        <v>11.0903565092398</v>
       </c>
       <c r="C42" s="0">
-        <v>26.180725903890899</v>
+        <v>26.180713018479501</v>
       </c>
       <c r="D42" s="0">
-        <v>29.923127925706702</v>
+        <v>29.923115040295301</v>
       </c>
       <c r="E42" s="0">
-        <v>22.180717776545301</v>
+        <v>22.1807177716856</v>
       </c>
       <c r="F42" s="0">
-        <v>50.361435553090601</v>
+        <v>50.361435543371101</v>
       </c>
       <c r="G42" s="0">
-        <v>55.975038585814303</v>
+        <v>55.975038576094803</v>
       </c>
       <c r="H42" s="0">
-        <v>11.0903565006771</v>
+        <v>11.090395373022201</v>
       </c>
       <c r="I42" s="0">
-        <v>28.180713001354199</v>
+        <v>28.180790746044401</v>
       </c>
       <c r="J42" s="0">
-        <v>33.794316034077902</v>
+        <v>33.794393778768097</v>
       </c>
       <c r="K42" s="0">
-        <v>22.180711383534899</v>
+        <v>22.180749771251399</v>
       </c>
       <c r="L42" s="0">
-        <v>52.361422767069797</v>
+        <v>52.361499542502699</v>
       </c>
       <c r="M42" s="0">
-        <v>59.846226810701303</v>
+        <v>59.846303586134297</v>
       </c>
       <c r="N42" s="0">
-        <v>5.0264895789538002</v>
+        <v>11.090356543113201</v>
       </c>
       <c r="O42" s="0">
-        <v>14.0529791579076</v>
+        <v>26.180713086226401</v>
       </c>
       <c r="P42" s="0">
-        <v>17.7953811797234</v>
+        <v>29.9231151080422</v>
       </c>
       <c r="Q42" s="0">
-        <v>20.314917162300102</v>
+        <v>22.180717742754201</v>
       </c>
       <c r="R42" s="0">
-        <v>46.629834324600203</v>
+        <v>50.361435485508501</v>
       </c>
       <c r="S42" s="0">
-        <v>52.243437357323899</v>
+        <v>55.975038518232203</v>
       </c>
       <c r="T42" s="0">
-        <v>9.2245622733401405</v>
+        <v>11.090362974906499</v>
       </c>
       <c r="U42" s="0">
-        <v>24.449124546680299</v>
+        <v>28.180725949812999</v>
       </c>
       <c r="V42" s="0">
-        <v>30.062727579404001</v>
+        <v>33.794328982536697</v>
       </c>
       <c r="W42" s="0">
-        <v>20.314917162298901</v>
+        <v>22.1807105187746</v>
       </c>
       <c r="X42" s="0">
-        <v>48.629834324597802</v>
+        <v>52.361421037549299</v>
       </c>
       <c r="Y42" s="0">
-        <v>56.1146383682294</v>
+        <v>59.846225081180798</v>
       </c>
       <c r="Z42" s="0">
-        <v>-0</v>
+        <v>11.0903565065754</v>
       </c>
       <c r="AA42" s="0">
-        <v>4</v>
+        <v>26.180713013150701</v>
       </c>
       <c r="AB42" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231150349665</v>
       </c>
       <c r="AC42" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180749569049599</v>
       </c>
       <c r="AD42" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361499138099198</v>
       </c>
       <c r="AE42" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751021708229</v>
       </c>
       <c r="AF42" s="0">
-        <v>-0</v>
+        <v>11.0903630001708</v>
       </c>
       <c r="AG42" s="0">
-        <v>6</v>
+        <v>28.1807260003416</v>
       </c>
       <c r="AH42" s="0">
-        <v>11.613603032723701</v>
+        <v>33.794329033065203</v>
       </c>
       <c r="AI42" s="0">
-        <v>16.6355323334387</v>
+        <v>22.1807123848203</v>
       </c>
       <c r="AJ42" s="0">
-        <v>41.2710646668774</v>
+        <v>52.3614247696406</v>
       </c>
       <c r="AK42" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846228813272198</v>
       </c>
       <c r="AL42" s="0">
         <v>1</v>
@@ -5092,112 +5092,112 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>32.565635211804498</v>
+        <v>32.186452029982398</v>
       </c>
       <c r="C43" s="0">
-        <v>69.131270423608896</v>
+        <v>68.372904059964895</v>
       </c>
       <c r="D43" s="0">
-        <v>72.873672445424702</v>
+        <v>72.115306081780602</v>
       </c>
       <c r="E43" s="0">
-        <v>33.115444565616997</v>
+        <v>33.032529611371302</v>
       </c>
       <c r="F43" s="0">
-        <v>72.230889131233894</v>
+        <v>72.065059222742605</v>
       </c>
       <c r="G43" s="0">
-        <v>77.844492163957597</v>
+        <v>77.678662255466307</v>
       </c>
       <c r="H43" s="0">
-        <v>33.271064686877402</v>
+        <v>33.144465039412601</v>
       </c>
       <c r="I43" s="0">
-        <v>72.542129373754705</v>
+        <v>72.288930078825302</v>
       </c>
       <c r="J43" s="0">
-        <v>78.155732406478407</v>
+        <v>77.902533111548905</v>
       </c>
       <c r="K43" s="0">
-        <v>33.115444326722702</v>
+        <v>33.032529675373802</v>
       </c>
       <c r="L43" s="0">
-        <v>74.230888653445405</v>
+        <v>74.065059350747603</v>
       </c>
       <c r="M43" s="0">
-        <v>81.715692697076904</v>
+        <v>81.549863394379202</v>
       </c>
       <c r="N43" s="0">
-        <v>31.049948606137601</v>
+        <v>32.228857248829897</v>
       </c>
       <c r="O43" s="0">
-        <v>66.099897212275195</v>
+        <v>68.457714497659893</v>
       </c>
       <c r="P43" s="0">
-        <v>69.842299234091001</v>
+        <v>72.200116519475699</v>
       </c>
       <c r="Q43" s="0">
-        <v>32.809819811840001</v>
+        <v>33.117590901240803</v>
       </c>
       <c r="R43" s="0">
-        <v>71.619639623680001</v>
+        <v>72.235181802481705</v>
       </c>
       <c r="S43" s="0">
-        <v>77.233242656403604</v>
+        <v>77.848784835205294</v>
       </c>
       <c r="T43" s="0">
-        <v>31.1325934297125</v>
+        <v>33.271064746877201</v>
       </c>
       <c r="U43" s="0">
-        <v>68.265186859424901</v>
+        <v>72.542129493754302</v>
       </c>
       <c r="V43" s="0">
-        <v>73.878789892148603</v>
+        <v>78.155732526478005</v>
       </c>
       <c r="W43" s="0">
-        <v>32.8098198134822</v>
+        <v>33.117590662276903</v>
       </c>
       <c r="X43" s="0">
-        <v>73.619639626964499</v>
+        <v>74.235181324553693</v>
       </c>
       <c r="Y43" s="0">
-        <v>81.104443670595998</v>
+        <v>81.719985368185306</v>
       </c>
       <c r="Z43" s="0">
-        <v>31.139667324031599</v>
+        <v>32.2359264678133</v>
       </c>
       <c r="AA43" s="0">
-        <v>66.279334648063099</v>
+        <v>68.4718529356266</v>
       </c>
       <c r="AB43" s="0">
-        <v>70.021736669878905</v>
+        <v>72.214254957442407</v>
       </c>
       <c r="AC43" s="0">
-        <v>32.799415281844603</v>
+        <v>33.207518163693202</v>
       </c>
       <c r="AD43" s="0">
-        <v>71.598830563689106</v>
+        <v>72.415036327386503</v>
       </c>
       <c r="AE43" s="0">
-        <v>77.212433596412794</v>
+        <v>78.028639360110105</v>
       </c>
       <c r="AF43" s="0">
-        <v>30.9297998757615</v>
+        <v>33.271065066880503</v>
       </c>
       <c r="AG43" s="0">
-        <v>67.859599751522893</v>
+        <v>72.542130133761106</v>
       </c>
       <c r="AH43" s="0">
-        <v>73.473202784246595</v>
+        <v>78.155733166484794</v>
       </c>
       <c r="AI43" s="0">
-        <v>32.7994152851781</v>
+        <v>33.207518099693303</v>
       </c>
       <c r="AJ43" s="0">
-        <v>73.598830570356199</v>
+        <v>74.415036199386506</v>
       </c>
       <c r="AK43" s="0">
-        <v>81.083634613987698</v>
+        <v>81.899840243018105</v>
       </c>
       <c r="AL43" s="0">
         <v>1</v>
@@ -5208,112 +5208,112 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C44" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D44" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E44" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F44" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G44" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H44" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I44" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J44" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K44" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L44" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M44" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N44" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O44" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P44" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q44" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R44" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S44" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T44" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U44" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V44" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W44" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X44" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y44" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z44" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA44" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB44" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC44" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD44" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE44" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF44" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG44" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH44" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI44" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ44" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK44" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL44" s="0">
         <v>1</v>
@@ -5324,112 +5324,112 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>23.8834503365212</v>
+        <v>23.883451936523301</v>
       </c>
       <c r="C45" s="0">
-        <v>51.7669006730424</v>
+        <v>51.766903873046502</v>
       </c>
       <c r="D45" s="0">
-        <v>55.5093026948581</v>
+        <v>55.509305894862301</v>
       </c>
       <c r="E45" s="0">
-        <v>31.367183474121699</v>
+        <v>31.367183474120601</v>
       </c>
       <c r="F45" s="0">
-        <v>68.734366948243405</v>
+        <v>68.734366948241203</v>
       </c>
       <c r="G45" s="0">
-        <v>74.347969980967093</v>
+        <v>74.347969980964805</v>
       </c>
       <c r="H45" s="0">
-        <v>23.8834503365226</v>
+        <v>23.883450336548201</v>
       </c>
       <c r="I45" s="0">
-        <v>53.7669006730451</v>
+        <v>53.766900673096302</v>
       </c>
       <c r="J45" s="0">
-        <v>59.380503705768803</v>
+        <v>59.380503705819997</v>
       </c>
       <c r="K45" s="0">
-        <v>31.3671834741235</v>
+        <v>31.3671818741214</v>
       </c>
       <c r="L45" s="0">
-        <v>70.7343669482471</v>
+        <v>70.734363748242799</v>
       </c>
       <c r="M45" s="0">
-        <v>78.219170991878698</v>
+        <v>78.219167791874298</v>
       </c>
       <c r="N45" s="0">
-        <v>23.021715971574999</v>
+        <v>23.883450936398098</v>
       </c>
       <c r="O45" s="0">
-        <v>50.043431943149997</v>
+        <v>51.766901872796304</v>
       </c>
       <c r="P45" s="0">
-        <v>53.785833964965697</v>
+        <v>55.509303894612003</v>
       </c>
       <c r="Q45" s="0">
-        <v>27.6736868203303</v>
+        <v>31.367181494127902</v>
       </c>
       <c r="R45" s="0">
-        <v>61.347373640660599</v>
+        <v>68.734362988255697</v>
       </c>
       <c r="S45" s="0">
-        <v>66.960976673384295</v>
+        <v>74.347966020979399</v>
       </c>
       <c r="T45" s="0">
-        <v>22.808152049217401</v>
+        <v>23.8834519373791</v>
       </c>
       <c r="U45" s="0">
-        <v>51.616304098434803</v>
+        <v>53.766903874758299</v>
       </c>
       <c r="V45" s="0">
-        <v>57.229907131158498</v>
+        <v>59.380506907482001</v>
       </c>
       <c r="W45" s="0">
-        <v>27.673686820383001</v>
+        <v>31.367181494126701</v>
       </c>
       <c r="X45" s="0">
-        <v>63.347373640766001</v>
+        <v>70.734362988253494</v>
       </c>
       <c r="Y45" s="0">
-        <v>70.832177684397607</v>
+        <v>78.219167031884993</v>
       </c>
       <c r="Z45" s="0">
-        <v>22.916245271989901</v>
+        <v>23.883450336553501</v>
       </c>
       <c r="AA45" s="0">
-        <v>49.832490543979901</v>
+        <v>51.766900673107003</v>
       </c>
       <c r="AB45" s="0">
-        <v>53.5748925657957</v>
+        <v>55.509302694922702</v>
       </c>
       <c r="AC45" s="0">
-        <v>28.317294911403099</v>
+        <v>31.367183474121902</v>
       </c>
       <c r="AD45" s="0">
-        <v>62.634589822806298</v>
+        <v>68.734366948243903</v>
       </c>
       <c r="AE45" s="0">
-        <v>68.248192855529894</v>
+        <v>74.347969980967605</v>
       </c>
       <c r="AF45" s="0">
-        <v>23.809993585514601</v>
+        <v>23.8834519365098</v>
       </c>
       <c r="AG45" s="0">
-        <v>53.619987171029202</v>
+        <v>53.7669038730197</v>
       </c>
       <c r="AH45" s="0">
-        <v>59.233590203752897</v>
+        <v>59.380506905743303</v>
       </c>
       <c r="AI45" s="0">
-        <v>28.317294938048398</v>
+        <v>31.367181554120901</v>
       </c>
       <c r="AJ45" s="0">
-        <v>64.634589876096896</v>
+        <v>70.734363108241794</v>
       </c>
       <c r="AK45" s="0">
-        <v>72.119393919728395</v>
+        <v>78.219167151873407</v>
       </c>
       <c r="AL45" s="0">
         <v>1</v>
@@ -5440,112 +5440,112 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>32.868771272478497</v>
+        <v>32.868771272475399</v>
       </c>
       <c r="C46" s="0">
-        <v>69.737542544956995</v>
+        <v>69.737542544950898</v>
       </c>
       <c r="D46" s="0">
-        <v>73.479944566772701</v>
+        <v>73.479944566766704</v>
       </c>
       <c r="E46" s="0">
-        <v>32.815162130738997</v>
+        <v>32.815162130728098</v>
       </c>
       <c r="F46" s="0">
-        <v>71.630324261477995</v>
+        <v>71.630324261456195</v>
       </c>
       <c r="G46" s="0">
-        <v>77.243927294201697</v>
+        <v>77.243927294179898</v>
       </c>
       <c r="H46" s="0">
-        <v>32.868771272478902</v>
+        <v>32.8687712724793</v>
       </c>
       <c r="I46" s="0">
-        <v>71.737542544957705</v>
+        <v>71.7375425449586</v>
       </c>
       <c r="J46" s="0">
-        <v>77.351145577681393</v>
+        <v>77.351145577682303</v>
       </c>
       <c r="K46" s="0">
-        <v>32.815162130736603</v>
+        <v>32.815162130727202</v>
       </c>
       <c r="L46" s="0">
-        <v>73.630324261473206</v>
+        <v>73.630324261454405</v>
       </c>
       <c r="M46" s="0">
-        <v>81.115128305104804</v>
+        <v>81.115128305086003</v>
       </c>
       <c r="N46" s="0">
-        <v>30.991901222288199</v>
+        <v>32.868769292483798</v>
       </c>
       <c r="O46" s="0">
-        <v>65.983802444576497</v>
+        <v>69.737538584967595</v>
       </c>
       <c r="P46" s="0">
-        <v>69.726204466392204</v>
+        <v>73.479940606783401</v>
       </c>
       <c r="Q46" s="0">
-        <v>31.308647793229099</v>
+        <v>32.815160210818398</v>
       </c>
       <c r="R46" s="0">
-        <v>68.617295586458198</v>
+        <v>71.630320421636796</v>
       </c>
       <c r="S46" s="0">
-        <v>74.230898619181801</v>
+        <v>77.243923454360498</v>
       </c>
       <c r="T46" s="0">
-        <v>31.308647793106299</v>
+        <v>32.868769672590503</v>
       </c>
       <c r="U46" s="0">
-        <v>68.617295586212606</v>
+        <v>71.737539345180906</v>
       </c>
       <c r="V46" s="0">
-        <v>74.230898618936294</v>
+        <v>77.351142377904594</v>
       </c>
       <c r="W46" s="0">
-        <v>31.3086477930329</v>
+        <v>32.815160210834101</v>
       </c>
       <c r="X46" s="0">
-        <v>70.617295586065794</v>
+        <v>73.630320421668301</v>
       </c>
       <c r="Y46" s="0">
-        <v>78.102099629697406</v>
+        <v>81.1151244652998</v>
       </c>
       <c r="Z46" s="0">
-        <v>31.444284386403702</v>
+        <v>32.8687712724779</v>
       </c>
       <c r="AA46" s="0">
-        <v>66.888568772807403</v>
+        <v>69.7375425449559</v>
       </c>
       <c r="AB46" s="0">
-        <v>70.630970794623195</v>
+        <v>73.479944566771593</v>
       </c>
       <c r="AC46" s="0">
-        <v>29.111689574245499</v>
+        <v>32.815160210739798</v>
       </c>
       <c r="AD46" s="0">
-        <v>64.223379148491006</v>
+        <v>71.630320421479496</v>
       </c>
       <c r="AE46" s="0">
-        <v>69.836982181214694</v>
+        <v>77.243923454203198</v>
       </c>
       <c r="AF46" s="0">
-        <v>29.104924801071402</v>
+        <v>32.868769352471297</v>
       </c>
       <c r="AG46" s="0">
-        <v>64.209849602142697</v>
+        <v>71.737538704942594</v>
       </c>
       <c r="AH46" s="0">
-        <v>69.823452634866399</v>
+        <v>77.351141737666197</v>
       </c>
       <c r="AI46" s="0">
-        <v>29.111689564711401</v>
+        <v>32.8151601467397</v>
       </c>
       <c r="AJ46" s="0">
-        <v>66.223379129422895</v>
+        <v>73.6303202934794</v>
       </c>
       <c r="AK46" s="0">
-        <v>73.708183173054493</v>
+        <v>81.115124337110899</v>
       </c>
       <c r="AL46" s="0">
         <v>1</v>
@@ -5556,112 +5556,112 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C47" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D47" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E47" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F47" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G47" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H47" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I47" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J47" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K47" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L47" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M47" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N47" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O47" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P47" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q47" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R47" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S47" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T47" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U47" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V47" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W47" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X47" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y47" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z47" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA47" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB47" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC47" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD47" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE47" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF47" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG47" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH47" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI47" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ47" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK47" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL47" s="0">
         <v>1</v>
@@ -5672,112 +5672,112 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>21.071647862818399</v>
+        <v>21.071647862892601</v>
       </c>
       <c r="C48" s="0">
-        <v>46.143295725636897</v>
+        <v>46.143295725785201</v>
       </c>
       <c r="D48" s="0">
-        <v>49.885697747452603</v>
+        <v>49.885697747601</v>
       </c>
       <c r="E48" s="0">
-        <v>22.180749782467601</v>
+        <v>22.180715681132199</v>
       </c>
       <c r="F48" s="0">
-        <v>50.361499564935301</v>
+        <v>50.361431362264497</v>
       </c>
       <c r="G48" s="0">
-        <v>55.975102597659003</v>
+        <v>55.975034394988199</v>
       </c>
       <c r="H48" s="0">
-        <v>21.071649462817501</v>
+        <v>21.071647862852501</v>
       </c>
       <c r="I48" s="0">
-        <v>48.143298925634902</v>
+        <v>48.143295725705002</v>
       </c>
       <c r="J48" s="0">
-        <v>53.756901958358597</v>
+        <v>53.756898758428697</v>
       </c>
       <c r="K48" s="0">
-        <v>22.180709858639201</v>
+        <v>22.1807113791006</v>
       </c>
       <c r="L48" s="0">
-        <v>52.361419717278402</v>
+        <v>52.361422758201201</v>
       </c>
       <c r="M48" s="0">
-        <v>59.846223760909901</v>
+        <v>59.846226801832799</v>
       </c>
       <c r="N48" s="0">
-        <v>20.049753086016601</v>
+        <v>21.071649514005198</v>
       </c>
       <c r="O48" s="0">
-        <v>44.099506172033301</v>
+        <v>46.143299028010297</v>
       </c>
       <c r="P48" s="0">
-        <v>47.8419081938491</v>
+        <v>49.885701049826103</v>
       </c>
       <c r="Q48" s="0">
-        <v>21.8745488749943</v>
+        <v>22.180717827393501</v>
       </c>
       <c r="R48" s="0">
-        <v>49.749097749988501</v>
+        <v>50.361435654786902</v>
       </c>
       <c r="S48" s="0">
-        <v>55.362700782712203</v>
+        <v>55.975038687510597</v>
       </c>
       <c r="T48" s="0">
-        <v>19.775903473476799</v>
+        <v>21.0716494628176</v>
       </c>
       <c r="U48" s="0">
-        <v>45.551806946953597</v>
+        <v>48.1432989256352</v>
       </c>
       <c r="V48" s="0">
-        <v>51.1654099796773</v>
+        <v>53.756901958358903</v>
       </c>
       <c r="W48" s="0">
-        <v>21.874548874994499</v>
+        <v>22.180717739368401</v>
       </c>
       <c r="X48" s="0">
-        <v>51.749097749988898</v>
+        <v>52.361435478736901</v>
       </c>
       <c r="Y48" s="0">
-        <v>59.233901793620497</v>
+        <v>59.8462395223684</v>
       </c>
       <c r="Z48" s="0">
-        <v>20.7210434992225</v>
+        <v>21.071647864550702</v>
       </c>
       <c r="AA48" s="0">
-        <v>45.442086998444999</v>
+        <v>46.143295729101403</v>
       </c>
       <c r="AB48" s="0">
-        <v>49.184489020260798</v>
+        <v>49.885697750917203</v>
       </c>
       <c r="AC48" s="0">
-        <v>21.842071081532001</v>
+        <v>22.180715887509301</v>
       </c>
       <c r="AD48" s="0">
-        <v>49.684142163064003</v>
+        <v>50.361431775018701</v>
       </c>
       <c r="AE48" s="0">
-        <v>55.297745195787599</v>
+        <v>55.975034807742396</v>
       </c>
       <c r="AF48" s="0">
-        <v>18.846406451566001</v>
+        <v>21.071657462825598</v>
       </c>
       <c r="AG48" s="0">
-        <v>43.692812903131902</v>
+        <v>48.143314925651097</v>
       </c>
       <c r="AH48" s="0">
-        <v>49.306415935855597</v>
+        <v>53.7569179583748</v>
       </c>
       <c r="AI48" s="0">
-        <v>21.8420710815269</v>
+        <v>22.180749853023599</v>
       </c>
       <c r="AJ48" s="0">
-        <v>51.684142163053799</v>
+        <v>52.361499706047198</v>
       </c>
       <c r="AK48" s="0">
-        <v>59.168946206685398</v>
+        <v>59.846303749678803</v>
       </c>
       <c r="AL48" s="0">
         <v>1</v>
@@ -5788,112 +5788,112 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>11.090362984738</v>
+        <v>11.090362988444699</v>
       </c>
       <c r="C49" s="0">
-        <v>26.1807259694761</v>
+        <v>26.180725976889502</v>
       </c>
       <c r="D49" s="0">
-        <v>29.923127991291899</v>
+        <v>29.923127998705201</v>
       </c>
       <c r="E49" s="0">
-        <v>22.180717773871201</v>
+        <v>22.180715615676501</v>
       </c>
       <c r="F49" s="0">
-        <v>50.361435547742502</v>
+        <v>50.361431231353102</v>
       </c>
       <c r="G49" s="0">
-        <v>55.975038580466098</v>
+        <v>55.975034264076797</v>
       </c>
       <c r="H49" s="0">
-        <v>11.090355291164499</v>
+        <v>11.090364603593001</v>
       </c>
       <c r="I49" s="0">
-        <v>28.180710582328999</v>
+        <v>28.180729207186101</v>
       </c>
       <c r="J49" s="0">
-        <v>33.794313615052701</v>
+        <v>33.794332239909799</v>
       </c>
       <c r="K49" s="0">
-        <v>22.180717791780001</v>
+        <v>22.180716799258299</v>
       </c>
       <c r="L49" s="0">
-        <v>52.361435583560002</v>
+        <v>52.361433598516697</v>
       </c>
       <c r="M49" s="0">
-        <v>59.846239627191501</v>
+        <v>59.846237642148303</v>
       </c>
       <c r="N49" s="0">
-        <v>6.6917218230053503</v>
+        <v>11.0903629854354</v>
       </c>
       <c r="O49" s="0">
-        <v>17.383443646010701</v>
+        <v>26.180725970870899</v>
       </c>
       <c r="P49" s="0">
-        <v>21.1258456678265</v>
+        <v>29.923127992686599</v>
       </c>
       <c r="Q49" s="0">
-        <v>21.295610051718398</v>
+        <v>22.180717773383101</v>
       </c>
       <c r="R49" s="0">
-        <v>48.591220103436903</v>
+        <v>50.361435546766103</v>
       </c>
       <c r="S49" s="0">
-        <v>54.204823136160599</v>
+        <v>55.975038579489798</v>
       </c>
       <c r="T49" s="0">
-        <v>10.205255162757901</v>
+        <v>11.0903630808724</v>
       </c>
       <c r="U49" s="0">
-        <v>26.410510325515901</v>
+        <v>28.180726161744701</v>
       </c>
       <c r="V49" s="0">
-        <v>32.024113358239603</v>
+        <v>33.794329194468403</v>
       </c>
       <c r="W49" s="0">
-        <v>21.295610051718199</v>
+        <v>22.1807178067445</v>
       </c>
       <c r="X49" s="0">
-        <v>50.591220103436399</v>
+        <v>52.3614356134891</v>
       </c>
       <c r="Y49" s="0">
-        <v>58.076024147067997</v>
+        <v>59.846239657120698</v>
       </c>
       <c r="Z49" s="0">
-        <v>-0</v>
+        <v>11.0903629873015</v>
       </c>
       <c r="AA49" s="0">
-        <v>4</v>
+        <v>26.180725974603099</v>
       </c>
       <c r="AB49" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127996418899</v>
       </c>
       <c r="AC49" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180711379302601</v>
       </c>
       <c r="AD49" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361422758605102</v>
       </c>
       <c r="AE49" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975025791328797</v>
       </c>
       <c r="AF49" s="0">
-        <v>-0</v>
+        <v>11.0903629890438</v>
       </c>
       <c r="AG49" s="0">
-        <v>6</v>
+        <v>28.180725978087601</v>
       </c>
       <c r="AH49" s="0">
-        <v>11.613603032723701</v>
+        <v>33.794329010811197</v>
       </c>
       <c r="AI49" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180716177685898</v>
       </c>
       <c r="AJ49" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361432355371797</v>
       </c>
       <c r="AK49" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846236399003402</v>
       </c>
       <c r="AL49" s="0">
         <v>1</v>
@@ -5904,112 +5904,112 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>29.463298361366199</v>
+        <v>29.463298361367901</v>
       </c>
       <c r="C50" s="0">
-        <v>62.926596722732398</v>
+        <v>62.926596722735702</v>
       </c>
       <c r="D50" s="0">
-        <v>66.668998744548205</v>
+        <v>66.668998744551502</v>
       </c>
       <c r="E50" s="0">
-        <v>33.069918969677801</v>
+        <v>33.069918969678596</v>
       </c>
       <c r="F50" s="0">
-        <v>72.139837939355701</v>
+        <v>72.139837939357193</v>
       </c>
       <c r="G50" s="0">
-        <v>77.753440972079304</v>
+        <v>77.753440972080895</v>
       </c>
       <c r="H50" s="0">
-        <v>29.463298301371601</v>
+        <v>29.463300281362802</v>
       </c>
       <c r="I50" s="0">
-        <v>64.926596602743203</v>
+        <v>64.926600562725696</v>
       </c>
       <c r="J50" s="0">
-        <v>70.540199635466905</v>
+        <v>70.540203595449299</v>
       </c>
       <c r="K50" s="0">
-        <v>33.069918969676401</v>
+        <v>33.069917369679303</v>
       </c>
       <c r="L50" s="0">
-        <v>74.139837939352901</v>
+        <v>74.139834739358704</v>
       </c>
       <c r="M50" s="0">
-        <v>81.6246419829845</v>
+        <v>81.624638782990203</v>
       </c>
       <c r="N50" s="0">
-        <v>27.094735680244099</v>
+        <v>29.4633002813645</v>
       </c>
       <c r="O50" s="0">
-        <v>58.189471360488199</v>
+        <v>62.926600562729</v>
       </c>
       <c r="P50" s="0">
-        <v>61.931873382303898</v>
+        <v>66.6690025845447</v>
       </c>
       <c r="Q50" s="0">
-        <v>29.792731768786599</v>
+        <v>33.069917049679503</v>
       </c>
       <c r="R50" s="0">
-        <v>65.585463537573304</v>
+        <v>72.139834099359007</v>
       </c>
       <c r="S50" s="0">
-        <v>71.199066570296907</v>
+        <v>77.753437132082695</v>
       </c>
       <c r="T50" s="0">
-        <v>28.361719478401898</v>
+        <v>29.463298682607199</v>
       </c>
       <c r="U50" s="0">
-        <v>62.723438956803697</v>
+        <v>64.926597365214505</v>
       </c>
       <c r="V50" s="0">
-        <v>68.337041989527407</v>
+        <v>70.540200397938094</v>
       </c>
       <c r="W50" s="0">
-        <v>29.792731768759499</v>
+        <v>33.069918569678897</v>
       </c>
       <c r="X50" s="0">
-        <v>67.585463537518905</v>
+        <v>74.139837139357795</v>
       </c>
       <c r="Y50" s="0">
-        <v>75.070267581150503</v>
+        <v>81.624641182989293</v>
       </c>
       <c r="Z50" s="0">
-        <v>28.8954144824134</v>
+        <v>29.4632986813683</v>
       </c>
       <c r="AA50" s="0">
-        <v>61.790828964826801</v>
+        <v>62.926597362736601</v>
       </c>
       <c r="AB50" s="0">
-        <v>65.533230986642593</v>
+        <v>66.668999384552393</v>
       </c>
       <c r="AC50" s="0">
-        <v>32.4914004814027</v>
+        <v>33.069917369679601</v>
       </c>
       <c r="AD50" s="0">
-        <v>70.982800962805399</v>
+        <v>72.139834739359301</v>
       </c>
       <c r="AE50" s="0">
-        <v>76.596403995529101</v>
+        <v>77.753437772082904</v>
       </c>
       <c r="AF50" s="0">
-        <v>29.412630701724201</v>
+        <v>29.4126306983121</v>
       </c>
       <c r="AG50" s="0">
-        <v>64.825261403448394</v>
+        <v>64.8252613966241</v>
       </c>
       <c r="AH50" s="0">
-        <v>70.438864436172096</v>
+        <v>70.438864429347802</v>
       </c>
       <c r="AI50" s="0">
-        <v>32.491400500721902</v>
+        <v>33.069917049679702</v>
       </c>
       <c r="AJ50" s="0">
-        <v>72.982801001443704</v>
+        <v>74.139834099359305</v>
       </c>
       <c r="AK50" s="0">
-        <v>80.467605045075302</v>
+        <v>81.624638142990904</v>
       </c>
       <c r="AL50" s="0">
         <v>0</v>
@@ -6020,112 +6020,112 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>29.463298681365199</v>
+        <v>29.463298483290998</v>
       </c>
       <c r="C51" s="0">
-        <v>62.926597362730398</v>
+        <v>62.926596966581997</v>
       </c>
       <c r="D51" s="0">
-        <v>66.668999384546098</v>
+        <v>66.668998988397803</v>
       </c>
       <c r="E51" s="0">
-        <v>31.972954881935902</v>
+        <v>31.9729533619292</v>
       </c>
       <c r="F51" s="0">
-        <v>69.945909763871896</v>
+        <v>69.9459067238584</v>
       </c>
       <c r="G51" s="0">
-        <v>75.559512796595598</v>
+        <v>75.559509756582102</v>
       </c>
       <c r="H51" s="0">
-        <v>29.463298681364201</v>
+        <v>29.463298681364101</v>
       </c>
       <c r="I51" s="0">
-        <v>64.926597362728401</v>
+        <v>64.926597362728202</v>
       </c>
       <c r="J51" s="0">
-        <v>70.540200395452104</v>
+        <v>70.540200395451905</v>
       </c>
       <c r="K51" s="0">
-        <v>31.9729532979289</v>
+        <v>31.972954881923599</v>
       </c>
       <c r="L51" s="0">
-        <v>71.945906595857906</v>
+        <v>71.945909763847297</v>
       </c>
       <c r="M51" s="0">
-        <v>79.430710639489405</v>
+        <v>79.430713807478796</v>
       </c>
       <c r="N51" s="0">
-        <v>28.913003897104002</v>
+        <v>29.463298681435301</v>
       </c>
       <c r="O51" s="0">
-        <v>61.826007794208003</v>
+        <v>62.926597362870602</v>
       </c>
       <c r="P51" s="0">
-        <v>65.568409816023802</v>
+        <v>66.668999384686401</v>
       </c>
       <c r="Q51" s="0">
-        <v>31.925071544647501</v>
+        <v>31.972953681928001</v>
       </c>
       <c r="R51" s="0">
-        <v>69.850143089295003</v>
+        <v>69.945907363855994</v>
       </c>
       <c r="S51" s="0">
-        <v>75.463746122018705</v>
+        <v>75.559510396579697</v>
       </c>
       <c r="T51" s="0">
-        <v>29.463038718901</v>
+        <v>29.463038718701899</v>
       </c>
       <c r="U51" s="0">
-        <v>64.926077437802107</v>
+        <v>64.926077437403904</v>
       </c>
       <c r="V51" s="0">
-        <v>70.539680470525795</v>
+        <v>70.539680470127607</v>
       </c>
       <c r="W51" s="0">
-        <v>31.925071542269698</v>
+        <v>31.972953681927901</v>
       </c>
       <c r="X51" s="0">
-        <v>71.850143084539297</v>
+        <v>71.945907363855795</v>
       </c>
       <c r="Y51" s="0">
-        <v>79.334947128170896</v>
+        <v>79.430711407487294</v>
       </c>
       <c r="Z51" s="0">
-        <v>28.620125362527101</v>
+        <v>29.463298681370301</v>
       </c>
       <c r="AA51" s="0">
-        <v>61.240250725054203</v>
+        <v>62.926597362740601</v>
       </c>
       <c r="AB51" s="0">
-        <v>64.982652746870002</v>
+        <v>66.6689993845564</v>
       </c>
       <c r="AC51" s="0">
-        <v>31.494802463291698</v>
+        <v>31.972953361886201</v>
       </c>
       <c r="AD51" s="0">
-        <v>68.989604926583397</v>
+        <v>69.945906723772396</v>
       </c>
       <c r="AE51" s="0">
-        <v>74.603207959307099</v>
+        <v>75.559509756495999</v>
       </c>
       <c r="AF51" s="0">
-        <v>29.4572724953007</v>
+        <v>29.463298366335199</v>
       </c>
       <c r="AG51" s="0">
-        <v>64.914544990601399</v>
+        <v>64.926596732670404</v>
       </c>
       <c r="AH51" s="0">
-        <v>70.528148023325102</v>
+        <v>70.540199765393993</v>
       </c>
       <c r="AI51" s="0">
-        <v>31.4948024420591</v>
+        <v>31.9729533618919</v>
       </c>
       <c r="AJ51" s="0">
-        <v>70.989604884118194</v>
+        <v>71.945906723783693</v>
       </c>
       <c r="AK51" s="0">
-        <v>78.474408927749707</v>
+        <v>79.430710767415306</v>
       </c>
       <c r="AL51" s="0">
         <v>0</v>
@@ -6136,112 +6136,112 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C52" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D52" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E52" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F52" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G52" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H52" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I52" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J52" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K52" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L52" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M52" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N52" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O52" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P52" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q52" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R52" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S52" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T52" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U52" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V52" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W52" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X52" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y52" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z52" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA52" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB52" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC52" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD52" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE52" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF52" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG52" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH52" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI52" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ52" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK52" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL52" s="0">
         <v>0</v>
@@ -6252,112 +6252,112 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C53" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D53" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E53" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F53" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G53" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H53" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I53" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J53" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K53" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L53" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M53" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N53" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O53" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P53" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q53" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R53" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S53" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T53" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U53" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V53" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W53" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X53" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y53" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z53" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA53" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB53" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC53" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD53" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE53" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF53" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG53" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH53" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI53" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ53" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK53" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL53" s="0">
         <v>0</v>
@@ -6368,112 +6368,112 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>17.3668726888158</v>
+        <v>17.366872688749599</v>
       </c>
       <c r="C54" s="0">
-        <v>38.7337453776316</v>
+        <v>38.733745377499098</v>
       </c>
       <c r="D54" s="0">
-        <v>42.476147399447399</v>
+        <v>42.476147399314897</v>
       </c>
       <c r="E54" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F54" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G54" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H54" s="0">
-        <v>17.366872690488702</v>
+        <v>17.366872688749801</v>
       </c>
       <c r="I54" s="0">
-        <v>40.733745380977297</v>
+        <v>40.733745377499503</v>
       </c>
       <c r="J54" s="0">
-        <v>46.347348413700999</v>
+        <v>46.347348410223198</v>
       </c>
       <c r="K54" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L54" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M54" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N54" s="0">
-        <v>15.219974607493601</v>
+        <v>17.366872688770499</v>
       </c>
       <c r="O54" s="0">
-        <v>34.439949214987301</v>
+        <v>38.733745377540998</v>
       </c>
       <c r="P54" s="0">
-        <v>38.182351236803001</v>
+        <v>42.476147399356798</v>
       </c>
       <c r="Q54" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R54" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S54" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T54" s="0">
-        <v>10.5358237314093</v>
+        <v>17.366874288749401</v>
       </c>
       <c r="U54" s="0">
-        <v>27.071647462818699</v>
+        <v>40.733748577498702</v>
       </c>
       <c r="V54" s="0">
-        <v>32.685250495542299</v>
+        <v>46.347351610222397</v>
       </c>
       <c r="W54" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X54" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y54" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z54" s="0">
-        <v>16.262848523629199</v>
+        <v>17.3668743087363</v>
       </c>
       <c r="AA54" s="0">
-        <v>36.525697047258397</v>
+        <v>38.7337486174725</v>
       </c>
       <c r="AB54" s="0">
-        <v>40.268099069074196</v>
+        <v>42.476150639288299</v>
       </c>
       <c r="AC54" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD54" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE54" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF54" s="0">
-        <v>11.869038548695</v>
+        <v>17.366872308752399</v>
       </c>
       <c r="AG54" s="0">
-        <v>29.738077097390001</v>
+        <v>40.733744617504897</v>
       </c>
       <c r="AH54" s="0">
-        <v>35.3516801301136</v>
+        <v>46.3473476502285</v>
       </c>
       <c r="AI54" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ54" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK54" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL54" s="0">
         <v>0</v>
@@ -6484,28 +6484,28 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>14.761030898602201</v>
+        <v>14.761030898602099</v>
       </c>
       <c r="C55" s="0">
         <v>33.522061797204302</v>
       </c>
       <c r="D55" s="0">
-        <v>37.264463819020101</v>
+        <v>37.264463819020001</v>
       </c>
       <c r="E55" s="0">
-        <v>25.110634909497101</v>
+        <v>25.1106349094972</v>
       </c>
       <c r="F55" s="0">
-        <v>56.221269818994202</v>
+        <v>56.221269818994401</v>
       </c>
       <c r="G55" s="0">
-        <v>61.834872851717797</v>
+        <v>61.834872851718103</v>
       </c>
       <c r="H55" s="0">
         <v>17.181381634835201</v>
       </c>
       <c r="I55" s="0">
-        <v>40.362763269670303</v>
+        <v>40.362763269670403</v>
       </c>
       <c r="J55" s="0">
         <v>45.976366302393998</v>
@@ -6520,76 +6520,76 @@
         <v>65.706073862625701</v>
       </c>
       <c r="N55" s="0">
-        <v>15.226796966711101</v>
+        <v>15.2267969658376</v>
       </c>
       <c r="O55" s="0">
-        <v>34.453593933422098</v>
+        <v>34.453593931675201</v>
       </c>
       <c r="P55" s="0">
-        <v>38.195995955237898</v>
+        <v>38.195995953491</v>
       </c>
       <c r="Q55" s="0">
-        <v>25.225644832900901</v>
+        <v>25.225644832457601</v>
       </c>
       <c r="R55" s="0">
-        <v>56.451289665801902</v>
+        <v>56.451289664915201</v>
       </c>
       <c r="S55" s="0">
-        <v>62.064892698525597</v>
+        <v>62.064892697638797</v>
       </c>
       <c r="T55" s="0">
-        <v>17.285917804513598</v>
+        <v>17.285917804292598</v>
       </c>
       <c r="U55" s="0">
-        <v>40.571835609027197</v>
+        <v>40.571835608585303</v>
       </c>
       <c r="V55" s="0">
-        <v>46.185438641750899</v>
+        <v>46.185438641308998</v>
       </c>
       <c r="W55" s="0">
-        <v>25.2256448328781</v>
+        <v>25.225644832457299</v>
       </c>
       <c r="X55" s="0">
-        <v>58.451289665756299</v>
+        <v>58.451289664914498</v>
       </c>
       <c r="Y55" s="0">
-        <v>65.936093709387805</v>
+        <v>65.936093708546096</v>
       </c>
       <c r="Z55" s="0">
-        <v>14.852034125248499</v>
+        <v>14.852034125036999</v>
       </c>
       <c r="AA55" s="0">
-        <v>33.704068250497002</v>
+        <v>33.704068250073902</v>
       </c>
       <c r="AB55" s="0">
-        <v>37.446470272312801</v>
+        <v>37.446470271889702</v>
       </c>
       <c r="AC55" s="0">
-        <v>25.0998969867927</v>
+        <v>25.099896986256699</v>
       </c>
       <c r="AD55" s="0">
-        <v>56.1997939735854</v>
+        <v>56.199793972513397</v>
       </c>
       <c r="AE55" s="0">
-        <v>61.813397006309103</v>
+        <v>61.8133970052371</v>
       </c>
       <c r="AF55" s="0">
-        <v>17.227579812756002</v>
+        <v>17.227579811129601</v>
       </c>
       <c r="AG55" s="0">
-        <v>40.455159625512003</v>
+        <v>40.455159622259302</v>
       </c>
       <c r="AH55" s="0">
-        <v>46.068762658235698</v>
+        <v>46.068762654982997</v>
       </c>
       <c r="AI55" s="0">
-        <v>25.099896986359099</v>
+        <v>25.099896986256699</v>
       </c>
       <c r="AJ55" s="0">
-        <v>58.199793972718297</v>
+        <v>58.199793972513397</v>
       </c>
       <c r="AK55" s="0">
-        <v>65.684598016349796</v>
+        <v>65.684598016145003</v>
       </c>
       <c r="AL55" s="0">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>14.893370735294001</v>
+        <v>14.8933707352941</v>
       </c>
       <c r="C56" s="0">
         <v>33.786741470588098</v>
@@ -6609,103 +6609,103 @@
         <v>37.529143492403897</v>
       </c>
       <c r="E56" s="0">
-        <v>25.318970497379802</v>
+        <v>25.318968879624698</v>
       </c>
       <c r="F56" s="0">
-        <v>56.637940994759703</v>
+        <v>56.637937759249503</v>
       </c>
       <c r="G56" s="0">
-        <v>62.251544027483298</v>
+        <v>62.251540791973099</v>
       </c>
       <c r="H56" s="0">
-        <v>14.8933707353138</v>
+        <v>14.893370735317699</v>
       </c>
       <c r="I56" s="0">
-        <v>35.786741470627597</v>
+        <v>35.786741470635398</v>
       </c>
       <c r="J56" s="0">
-        <v>41.400344503351199</v>
+        <v>41.400344503359101</v>
       </c>
       <c r="K56" s="0">
-        <v>25.318968557814401</v>
+        <v>25.318968877817198</v>
       </c>
       <c r="L56" s="0">
-        <v>58.637937115628901</v>
+        <v>58.637937755634397</v>
       </c>
       <c r="M56" s="0">
-        <v>66.1227411592604</v>
+        <v>66.122741799265896</v>
       </c>
       <c r="N56" s="0">
-        <v>5.5591688696789996</v>
+        <v>14.8933707352941</v>
       </c>
       <c r="O56" s="0">
-        <v>15.118337739357999</v>
+        <v>33.786741470588197</v>
       </c>
       <c r="P56" s="0">
-        <v>18.8607397611738</v>
+        <v>37.529143492404003</v>
       </c>
       <c r="Q56" s="0">
-        <v>21.0923464170058</v>
+        <v>25.318968877830901</v>
       </c>
       <c r="R56" s="0">
-        <v>48.184692834011599</v>
+        <v>56.637937755661703</v>
       </c>
       <c r="S56" s="0">
-        <v>53.798295866735302</v>
+        <v>62.251540788385398</v>
       </c>
       <c r="T56" s="0">
-        <v>11.8057056563127</v>
+        <v>14.893370735301501</v>
       </c>
       <c r="U56" s="0">
-        <v>29.611411312625499</v>
+        <v>35.786741470602898</v>
       </c>
       <c r="V56" s="0">
-        <v>35.225014345349102</v>
+        <v>41.4003445033266</v>
       </c>
       <c r="W56" s="0">
-        <v>21.092346416999199</v>
+        <v>25.318968877830901</v>
       </c>
       <c r="X56" s="0">
-        <v>50.184692833998497</v>
+        <v>58.637937755661802</v>
       </c>
       <c r="Y56" s="0">
-        <v>57.669496877630003</v>
+        <v>66.122741799293294</v>
       </c>
       <c r="Z56" s="0">
-        <v>7.5397673350498602</v>
+        <v>14.8933707352959</v>
       </c>
       <c r="AA56" s="0">
-        <v>19.079534670099701</v>
+        <v>33.7867414705917</v>
       </c>
       <c r="AB56" s="0">
-        <v>22.8219366919155</v>
+        <v>37.529143492407499</v>
       </c>
       <c r="AC56" s="0">
-        <v>21.939287295900801</v>
+        <v>25.318968497817</v>
       </c>
       <c r="AD56" s="0">
-        <v>49.878574591801602</v>
+        <v>56.637936995634099</v>
       </c>
       <c r="AE56" s="0">
-        <v>55.492177624525297</v>
+        <v>62.251540028357702</v>
       </c>
       <c r="AF56" s="0">
-        <v>12.7863646384238</v>
+        <v>14.8933723352933</v>
       </c>
       <c r="AG56" s="0">
-        <v>31.5727292768476</v>
+        <v>35.786744670586501</v>
       </c>
       <c r="AH56" s="0">
-        <v>37.186332309571199</v>
+        <v>41.400347703310203</v>
       </c>
       <c r="AI56" s="0">
-        <v>21.939287230601401</v>
+        <v>25.3189688778136</v>
       </c>
       <c r="AJ56" s="0">
-        <v>51.878574461202703</v>
+        <v>58.637937755627199</v>
       </c>
       <c r="AK56" s="0">
-        <v>59.363378504834301</v>
+        <v>66.122741799258804</v>
       </c>
       <c r="AL56" s="0">
         <v>0</v>
@@ -6725,103 +6725,103 @@
         <v>69.267088386830494</v>
       </c>
       <c r="E57" s="0">
-        <v>32.319743910666901</v>
+        <v>32.319743910667</v>
       </c>
       <c r="F57" s="0">
-        <v>70.639487821333802</v>
+        <v>70.6394878213341</v>
       </c>
       <c r="G57" s="0">
-        <v>76.253090854057504</v>
+        <v>76.253090854057703</v>
       </c>
       <c r="H57" s="0">
-        <v>31.967593907634502</v>
+        <v>31.967593907634001</v>
       </c>
       <c r="I57" s="0">
-        <v>69.935187815269003</v>
+        <v>69.935187815267994</v>
       </c>
       <c r="J57" s="0">
-        <v>75.548790847992606</v>
+        <v>75.548790847991697</v>
       </c>
       <c r="K57" s="0">
-        <v>32.3197439106671</v>
+        <v>32.319743910667</v>
       </c>
       <c r="L57" s="0">
-        <v>72.6394878213342</v>
+        <v>72.639487821334001</v>
       </c>
       <c r="M57" s="0">
-        <v>80.124291864965699</v>
+        <v>80.1242918649655</v>
       </c>
       <c r="N57" s="0">
-        <v>31.7882275250651</v>
+        <v>31.7882275200393</v>
       </c>
       <c r="O57" s="0">
-        <v>67.576455050130207</v>
+        <v>67.576455040078699</v>
       </c>
       <c r="P57" s="0">
-        <v>71.318857071945999</v>
+        <v>71.318857061894505</v>
       </c>
       <c r="Q57" s="0">
-        <v>32.427463554302904</v>
+        <v>32.427463554249897</v>
       </c>
       <c r="R57" s="0">
-        <v>70.854927108605906</v>
+        <v>70.854927108499794</v>
       </c>
       <c r="S57" s="0">
-        <v>76.468530141329595</v>
+        <v>76.468530141223496</v>
       </c>
       <c r="T57" s="0">
-        <v>32.022805116998299</v>
+        <v>32.022805116798402</v>
       </c>
       <c r="U57" s="0">
-        <v>70.045610233996598</v>
+        <v>70.045610233596804</v>
       </c>
       <c r="V57" s="0">
-        <v>75.6592132667203</v>
+        <v>75.659213266320506</v>
       </c>
       <c r="W57" s="0">
-        <v>32.427463554411403</v>
+        <v>32.427463554249101</v>
       </c>
       <c r="X57" s="0">
-        <v>72.854927108822807</v>
+        <v>72.854927108498302</v>
       </c>
       <c r="Y57" s="0">
-        <v>80.339731152454405</v>
+        <v>80.339731152129801</v>
       </c>
       <c r="Z57" s="0">
-        <v>31.4116099647925</v>
+        <v>31.411609964001801</v>
       </c>
       <c r="AA57" s="0">
-        <v>66.823219929584994</v>
+        <v>66.823219928003596</v>
       </c>
       <c r="AB57" s="0">
-        <v>70.5656219514008</v>
+        <v>70.565621949819402</v>
       </c>
       <c r="AC57" s="0">
-        <v>32.3607215160416</v>
+        <v>32.360721515847104</v>
       </c>
       <c r="AD57" s="0">
-        <v>70.721443032083101</v>
+        <v>70.721443031694207</v>
       </c>
       <c r="AE57" s="0">
-        <v>76.335046064806804</v>
+        <v>76.335046064417895</v>
       </c>
       <c r="AF57" s="0">
-        <v>32.019964210814301</v>
+        <v>32.019964210130397</v>
       </c>
       <c r="AG57" s="0">
-        <v>70.039928421628602</v>
+        <v>70.039928420260694</v>
       </c>
       <c r="AH57" s="0">
-        <v>75.653531454352304</v>
+        <v>75.653531452984396</v>
       </c>
       <c r="AI57" s="0">
-        <v>32.360721517233699</v>
+        <v>32.360721515846599</v>
       </c>
       <c r="AJ57" s="0">
-        <v>72.721443034467299</v>
+        <v>72.721443031693198</v>
       </c>
       <c r="AK57" s="0">
-        <v>80.206247078098897</v>
+        <v>80.206247075324796</v>
       </c>
       <c r="AL57" s="0">
         <v>0</v>
@@ -6832,112 +6832,112 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C58" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D58" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E58" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F58" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G58" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H58" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I58" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J58" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K58" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L58" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M58" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N58" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O58" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P58" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q58" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R58" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S58" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T58" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U58" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V58" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W58" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X58" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y58" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z58" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA58" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB58" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC58" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD58" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE58" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF58" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG58" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH58" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI58" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ58" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK58" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL58" s="0">
         <v>0</v>
@@ -6948,112 +6948,112 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C59" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D59" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E59" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F59" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G59" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H59" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I59" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J59" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K59" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L59" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M59" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N59" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O59" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P59" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q59" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R59" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S59" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T59" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U59" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V59" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W59" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X59" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y59" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z59" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA59" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB59" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC59" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD59" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE59" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF59" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG59" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH59" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI59" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ59" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK59" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL59" s="0">
         <v>0</v>
@@ -7064,112 +7064,112 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>11.090362975678801</v>
+        <v>11.090365454839199</v>
       </c>
       <c r="C60" s="0">
-        <v>26.180725951357601</v>
+        <v>26.180730909678498</v>
       </c>
       <c r="D60" s="0">
-        <v>29.923127973173401</v>
+        <v>29.923132931494301</v>
       </c>
       <c r="E60" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F60" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G60" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H60" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I60" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J60" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K60" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L60" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M60" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N60" s="0">
-        <v>3.9408358669711299</v>
+        <v>11.090362977654801</v>
       </c>
       <c r="O60" s="0">
-        <v>11.8816717339423</v>
+        <v>26.180725955309601</v>
       </c>
       <c r="P60" s="0">
-        <v>15.624073755758101</v>
+        <v>29.9231279771254</v>
       </c>
       <c r="Q60" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R60" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S60" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T60" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U60" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V60" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W60" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X60" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y60" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z60" s="0">
-        <v>-0</v>
+        <v>11.0903629756318</v>
       </c>
       <c r="AA60" s="0">
-        <v>4</v>
+        <v>26.1807259512637</v>
       </c>
       <c r="AB60" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127973079399</v>
       </c>
       <c r="AC60" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD60" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE60" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF60" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG60" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH60" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI60" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ60" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK60" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL60" s="0">
         <v>0</v>
@@ -7180,112 +7180,112 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>11.090362975678801</v>
+        <v>11.090365454839199</v>
       </c>
       <c r="C61" s="0">
-        <v>26.180725951357601</v>
+        <v>26.180730909678498</v>
       </c>
       <c r="D61" s="0">
-        <v>29.923127973173401</v>
+        <v>29.923132931494301</v>
       </c>
       <c r="E61" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F61" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G61" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H61" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I61" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J61" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K61" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L61" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M61" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N61" s="0">
-        <v>3.94083586697653</v>
+        <v>11.090362977654801</v>
       </c>
       <c r="O61" s="0">
-        <v>11.8816717339531</v>
+        <v>26.180725955309601</v>
       </c>
       <c r="P61" s="0">
-        <v>15.6240737557688</v>
+        <v>29.9231279771254</v>
       </c>
       <c r="Q61" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R61" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S61" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T61" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U61" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V61" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W61" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X61" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y61" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z61" s="0">
-        <v>-0</v>
+        <v>11.0903629756318</v>
       </c>
       <c r="AA61" s="0">
-        <v>4</v>
+        <v>26.1807259512637</v>
       </c>
       <c r="AB61" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127973079399</v>
       </c>
       <c r="AC61" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD61" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE61" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF61" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG61" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH61" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI61" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ61" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK61" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL61" s="0">
         <v>0</v>
@@ -7296,112 +7296,112 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C62" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D62" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E62" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F62" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G62" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H62" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I62" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J62" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K62" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L62" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M62" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N62" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O62" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P62" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q62" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R62" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S62" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T62" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U62" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V62" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W62" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X62" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y62" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z62" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA62" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB62" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC62" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD62" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE62" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF62" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG62" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH62" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI62" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ62" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK62" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL62" s="0">
         <v>0</v>
@@ -7412,112 +7412,112 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>11.0903630073764</v>
+        <v>11.0903647898652</v>
       </c>
       <c r="C63" s="0">
-        <v>26.180726014752899</v>
+        <v>26.180729579730301</v>
       </c>
       <c r="D63" s="0">
-        <v>29.923128036568698</v>
+        <v>29.9231316015461</v>
       </c>
       <c r="E63" s="0">
-        <v>22.180717786616899</v>
+        <v>22.1807177196171</v>
       </c>
       <c r="F63" s="0">
-        <v>50.361435573233798</v>
+        <v>50.3614354392341</v>
       </c>
       <c r="G63" s="0">
-        <v>55.975038605957501</v>
+        <v>55.975038471957802</v>
       </c>
       <c r="H63" s="0">
-        <v>11.090362834409101</v>
+        <v>11.090362985629699</v>
       </c>
       <c r="I63" s="0">
-        <v>28.180725668818301</v>
+        <v>28.180725971259399</v>
       </c>
       <c r="J63" s="0">
-        <v>33.7943287015419</v>
+        <v>33.794329003983101</v>
       </c>
       <c r="K63" s="0">
-        <v>22.180749638178401</v>
+        <v>22.180718588722002</v>
       </c>
       <c r="L63" s="0">
-        <v>52.361499276356902</v>
+        <v>52.361437177444003</v>
       </c>
       <c r="M63" s="0">
-        <v>59.846303319988401</v>
+        <v>59.846241221075601</v>
       </c>
       <c r="N63" s="0">
-        <v>-0</v>
+        <v>11.0903629872381</v>
       </c>
       <c r="O63" s="0">
-        <v>4</v>
+        <v>26.1807259744762</v>
       </c>
       <c r="P63" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.9231279962919</v>
       </c>
       <c r="Q63" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180717781307301</v>
       </c>
       <c r="R63" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361435562614702</v>
       </c>
       <c r="S63" s="0">
-        <v>44.884667699601003</v>
+        <v>55.975038595338397</v>
       </c>
       <c r="T63" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090362998904499</v>
       </c>
       <c r="U63" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180725997808999</v>
       </c>
       <c r="V63" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794329030532701</v>
       </c>
       <c r="W63" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180723797755199</v>
       </c>
       <c r="X63" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361447595510498</v>
       </c>
       <c r="Y63" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846251639141997</v>
       </c>
       <c r="Z63" s="0">
-        <v>-0</v>
+        <v>11.090362986176499</v>
       </c>
       <c r="AA63" s="0">
-        <v>4</v>
+        <v>26.180725972353098</v>
       </c>
       <c r="AB63" s="0">
-        <v>7.7424020218157796</v>
+        <v>29.923127994168901</v>
       </c>
       <c r="AC63" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180753809002098</v>
       </c>
       <c r="AD63" s="0">
-        <v>39.2710646668774</v>
+        <v>50.361507618004097</v>
       </c>
       <c r="AE63" s="0">
-        <v>44.884667699601003</v>
+        <v>55.9751106507278</v>
       </c>
       <c r="AF63" s="0">
-        <v>5.5451774444795596</v>
+        <v>11.090356513025601</v>
       </c>
       <c r="AG63" s="0">
-        <v>17.090354888959101</v>
+        <v>28.180713026051301</v>
       </c>
       <c r="AH63" s="0">
-        <v>22.7039579216828</v>
+        <v>33.794316058775003</v>
       </c>
       <c r="AI63" s="0">
-        <v>16.6355323334387</v>
+        <v>22.180710119040398</v>
       </c>
       <c r="AJ63" s="0">
-        <v>41.2710646668774</v>
+        <v>52.361420238080797</v>
       </c>
       <c r="AK63" s="0">
-        <v>48.755868710508899</v>
+        <v>59.846224281712402</v>
       </c>
       <c r="AL63" s="0">
         <v>0</v>
@@ -7528,112 +7528,112 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>28.752872650676501</v>
+        <v>28.752872650676299</v>
       </c>
       <c r="C64" s="0">
-        <v>61.505745301353102</v>
+        <v>61.505745301352697</v>
       </c>
       <c r="D64" s="0">
-        <v>65.248147323168894</v>
+        <v>65.248147323168496</v>
       </c>
       <c r="E64" s="0">
-        <v>30.6184189547598</v>
+        <v>30.618420935046601</v>
       </c>
       <c r="F64" s="0">
-        <v>67.236837909519593</v>
+        <v>67.236841870093301</v>
       </c>
       <c r="G64" s="0">
-        <v>72.850440942243296</v>
+        <v>72.850444902816903</v>
       </c>
       <c r="H64" s="0">
-        <v>28.752872650780301</v>
+        <v>28.7528710504595</v>
       </c>
       <c r="I64" s="0">
-        <v>63.505745301560701</v>
+        <v>63.505742100919001</v>
       </c>
       <c r="J64" s="0">
-        <v>69.119348334284297</v>
+        <v>69.119345133642696</v>
       </c>
       <c r="K64" s="0">
-        <v>30.6184209347627</v>
+        <v>30.618420935052299</v>
       </c>
       <c r="L64" s="0">
-        <v>69.236841869525506</v>
+        <v>69.236841870104698</v>
       </c>
       <c r="M64" s="0">
-        <v>76.721645913157005</v>
+        <v>76.721645913736197</v>
       </c>
       <c r="N64" s="0">
-        <v>20.075165471166699</v>
+        <v>28.752872656120299</v>
       </c>
       <c r="O64" s="0">
-        <v>44.150330942333397</v>
+        <v>61.505745312240599</v>
       </c>
       <c r="P64" s="0">
-        <v>47.892732964149197</v>
+        <v>65.248147334056398</v>
       </c>
       <c r="Q64" s="0">
-        <v>24.650079457199599</v>
+        <v>30.618419334759501</v>
       </c>
       <c r="R64" s="0">
-        <v>55.300158914399198</v>
+        <v>67.236838669518903</v>
       </c>
       <c r="S64" s="0">
-        <v>60.9137619471229</v>
+        <v>72.850441702242605</v>
       </c>
       <c r="T64" s="0">
-        <v>23.968233745530799</v>
+        <v>28.752872650445301</v>
       </c>
       <c r="U64" s="0">
-        <v>53.936467491061599</v>
+        <v>63.505745300890702</v>
       </c>
       <c r="V64" s="0">
-        <v>59.550070523785301</v>
+        <v>69.119348333614298</v>
       </c>
       <c r="W64" s="0">
-        <v>24.650079457185299</v>
+        <v>30.618419335983301</v>
       </c>
       <c r="X64" s="0">
-        <v>57.300158914370598</v>
+        <v>69.236838671966694</v>
       </c>
       <c r="Y64" s="0">
-        <v>64.784962958002197</v>
+        <v>76.721642715598307</v>
       </c>
       <c r="Z64" s="0">
-        <v>21.178119347604699</v>
+        <v>28.752871050437498</v>
       </c>
       <c r="AA64" s="0">
-        <v>46.356238695209399</v>
+        <v>61.505742100874997</v>
       </c>
       <c r="AB64" s="0">
-        <v>50.098640717025098</v>
+        <v>65.248144122690803</v>
       </c>
       <c r="AC64" s="0">
-        <v>25.4485694249896</v>
+        <v>30.6184193347441</v>
       </c>
       <c r="AD64" s="0">
-        <v>56.8971388499792</v>
+        <v>67.236838669488193</v>
       </c>
       <c r="AE64" s="0">
-        <v>62.510741882702902</v>
+        <v>72.850441702211896</v>
       </c>
       <c r="AF64" s="0">
-        <v>23.804031534021199</v>
+        <v>28.752871050426201</v>
       </c>
       <c r="AG64" s="0">
-        <v>53.608063068042298</v>
+        <v>63.505742100852402</v>
       </c>
       <c r="AH64" s="0">
-        <v>59.221666100766001</v>
+        <v>69.119345133576104</v>
       </c>
       <c r="AI64" s="0">
-        <v>25.4485692987083</v>
+        <v>30.618419334760102</v>
       </c>
       <c r="AJ64" s="0">
-        <v>58.8971385974166</v>
+        <v>69.236838669520296</v>
       </c>
       <c r="AK64" s="0">
-        <v>66.381942641048198</v>
+        <v>76.721642713151795</v>
       </c>
       <c r="AL64" s="0">
         <v>0</v>
@@ -7644,112 +7644,112 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>17.366872688749801</v>
+        <v>17.366872688758999</v>
       </c>
       <c r="C65" s="0">
-        <v>38.733745377499602</v>
+        <v>38.733745377517998</v>
       </c>
       <c r="D65" s="0">
-        <v>42.476147399315401</v>
+        <v>42.476147399333797</v>
       </c>
       <c r="E65" s="0">
-        <v>27.1713561448489</v>
+        <v>27.171356464846699</v>
       </c>
       <c r="F65" s="0">
-        <v>60.342712289697701</v>
+        <v>60.342712929693498</v>
       </c>
       <c r="G65" s="0">
-        <v>65.956315322421403</v>
+        <v>65.956315962417193</v>
       </c>
       <c r="H65" s="0">
-        <v>17.366872688749702</v>
+        <v>17.3668726887757</v>
       </c>
       <c r="I65" s="0">
-        <v>40.733745377499503</v>
+        <v>40.7337453775515</v>
       </c>
       <c r="J65" s="0">
-        <v>46.347348410223198</v>
+        <v>46.347348410275103</v>
       </c>
       <c r="K65" s="0">
-        <v>27.1713564648709</v>
+        <v>27.171356464854298</v>
       </c>
       <c r="L65" s="0">
-        <v>62.3427129297419</v>
+        <v>62.342712929708497</v>
       </c>
       <c r="M65" s="0">
-        <v>69.827516973373406</v>
+        <v>69.827516973340096</v>
       </c>
       <c r="N65" s="0">
-        <v>7.5470742744312904</v>
+        <v>17.366872688755201</v>
       </c>
       <c r="O65" s="0">
-        <v>19.094148548862599</v>
+        <v>38.733745377510402</v>
       </c>
       <c r="P65" s="0">
-        <v>22.836550570678401</v>
+        <v>42.476147399326202</v>
       </c>
       <c r="Q65" s="0">
-        <v>22.5453899245143</v>
+        <v>27.1713580648515</v>
       </c>
       <c r="R65" s="0">
-        <v>51.0907798490286</v>
+        <v>60.342716129703099</v>
       </c>
       <c r="S65" s="0">
-        <v>56.704382881752302</v>
+        <v>65.956319162426794</v>
       </c>
       <c r="T65" s="0">
-        <v>14.6260740362662</v>
+        <v>17.366874288748999</v>
       </c>
       <c r="U65" s="0">
-        <v>35.2521480725323</v>
+        <v>40.733748577497998</v>
       </c>
       <c r="V65" s="0">
-        <v>40.865751105256003</v>
+        <v>46.3473516102217</v>
       </c>
       <c r="W65" s="0">
-        <v>22.5453899245143</v>
+        <v>27.171356084851698</v>
       </c>
       <c r="X65" s="0">
-        <v>53.0907798490286</v>
+        <v>62.342712169703397</v>
       </c>
       <c r="Y65" s="0">
-        <v>60.575583892660198</v>
+        <v>69.827516213334903</v>
       </c>
       <c r="Z65" s="0">
-        <v>8.6994862039907606</v>
+        <v>17.366872688752</v>
       </c>
       <c r="AA65" s="0">
-        <v>21.3989724079815</v>
+        <v>38.733745377504</v>
       </c>
       <c r="AB65" s="0">
-        <v>25.141374429797299</v>
+        <v>42.4761473993198</v>
       </c>
       <c r="AC65" s="0">
-        <v>22.718191526277501</v>
+        <v>27.1713564660038</v>
       </c>
       <c r="AD65" s="0">
-        <v>51.436383052555001</v>
+        <v>60.342712932007601</v>
       </c>
       <c r="AE65" s="0">
-        <v>57.049986085278697</v>
+        <v>65.956315964731203</v>
       </c>
       <c r="AF65" s="0">
-        <v>14.839053366853999</v>
+        <v>17.3668726887574</v>
       </c>
       <c r="AG65" s="0">
-        <v>35.678106733708098</v>
+        <v>40.733745377514801</v>
       </c>
       <c r="AH65" s="0">
-        <v>41.291709766431801</v>
+        <v>46.347348410238503</v>
       </c>
       <c r="AI65" s="0">
-        <v>22.718191488774899</v>
+        <v>27.171356466131002</v>
       </c>
       <c r="AJ65" s="0">
-        <v>53.436382977549798</v>
+        <v>62.342712932262103</v>
       </c>
       <c r="AK65" s="0">
-        <v>60.921187021181296</v>
+        <v>69.827516975893602</v>
       </c>
       <c r="AL65" s="0">
         <v>0</v>
